--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -33,12 +33,17 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -68,9 +73,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -78,6 +83,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -517,10 +525,14 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>account table + AccountService + /accounts API + default UK chart (UK_SMALL_COMPANY v1). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: tests/api/ledger.test.ts (chart), tests/db/ledger.test.ts (account guards), packages/contracts/src/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -544,7 +556,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -577,7 +589,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -606,7 +618,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -635,7 +647,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -664,7 +676,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -693,7 +705,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -722,7 +734,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -751,7 +763,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -780,7 +792,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -809,7 +821,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -838,7 +850,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -873,11 +885,19 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>POST /journals (manual and opening-balance sources), GET /journals[/id], POST /journals/{id}/reverse; all through the PostingService. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Posting only: no draft or approval step for manual journals (open decision 5 in v1-plan.md)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -902,10 +922,14 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>GET /ledger (general ledger per account, running balance, keyset paging recomputed per page). Tests: tests/platform/posting-service.test.ts (one page equals paged), tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -931,10 +955,14 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>GET /reports/trial-balance (as at a date or a period with movement; journal lines only; balanced flag; suspense warning; drill-down parameters). Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts (independent SQL check)</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -958,7 +986,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -987,7 +1015,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1016,7 +1044,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1045,17 +1073,21 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>V0: accounting_period table with OPEN/CLOSED/LOCKED enum, no-overlap constraint, create/list API. No transition rules, no enforcement on postings.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>OPEN&lt;-&gt;CLOSED-&gt;LOCKED-&gt;CLOSED with database-enforced graph, period:manage / period:lock, mandatory reasons, audit before/after, events, concurrency-safe. Tests: tests/platform/posting-service.test.ts (period controls), tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Close controls beyond 'ledger balances' are added by M2-M5 as their data exists (see MAN-ACC-08)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1078,12 +1110,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>M1 delivers PostingService + journals + ledger with manual and reversal sources; each later milestone adds a transaction service</t>
@@ -1111,12 +1147,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Trial balance and general ledger aggregate journal_line only (architecture: no report reads source tables). P&amp;L and balance sheet are M5. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Trial balance in M1; statements in M5, both from journal lines only</t>
@@ -1146,10 +1186,14 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>account.code (unique per company, 1-20 chars). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1175,10 +1219,14 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>account.name. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1204,10 +1252,14 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>account.type (ASSET/LIABILITY/EQUITY/INCOME/EXPENSE). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1233,10 +1285,14 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>account.subtype (registry constrained to the type). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1262,10 +1318,14 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>account.is_control + control_kind (receivables, payables, VAT, bank, cash, suspense, retained earnings); manual journals cannot post to control accounts. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1291,10 +1351,14 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>account.tax_treatment (account level). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Account-level treatment in M1; VAT codes on lines arrive with the VAT foundation (M2)</t>
@@ -1324,10 +1388,14 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>account.reporting_mapping from a versioned report-line registry, checked against the type. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1353,10 +1421,14 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>account.active_from / active_to enforced on every posting date; deactivation cannot precede the last posting. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1382,13 +1454,17 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Single writer enforced three ways: architecture test (only packages/accounting/src/posting.ts writes journal/journal_line/ledger_sequence; only it sets app.posting; platform/AI/worker cannot import the package), database guard (insert refused without the transaction flag), privileges. Tests: tests/unit/architecture.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Enforced by an architecture test, a database guard (transaction flag) and privileges</t>
+          <t>Honest limit: the flag is application-asserted (same trust boundary as tenant context)</t>
         </is>
       </c>
     </row>
@@ -1415,10 +1491,14 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Application check + deferred constraint trigger at commit (header agrees with lines, contiguous numbering, reversal mirrors original). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1444,10 +1524,14 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Accounts must exist in the company (composite FK), be active on the journal date, and not be control accounts for manual sources. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1473,10 +1557,14 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Period must exist, contain the date and be OPEN; period row locked FOR SHARE so a concurrent close cannot race. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts (race test), tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1500,7 +1588,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1533,12 +1621,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Currency validated: journals are in the company base currency and amounts respect its minor units (application + database). Foreign-currency documents, FX rates and revaluation are NOT supported (open decision 1). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Base currency of the company only; foreign-currency postings and FX revaluation are not in V1 scope until a decision is recorded</t>
@@ -1568,10 +1660,14 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Registered source type required; REVERSAL must name the reversed journal; other sources require a source id; idempotency key per company with content hash. Tests: tests/platform/posting-service.test.ts, packages/contracts/src/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1597,10 +1693,14 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Source-specific permission evaluated for the journal's company through the central authoriser; AI actors refused; system actors limited to system sources. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts (roles x posting), tests/api/permissions.test.ts</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1624,7 +1724,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1653,7 +1753,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1682,7 +1782,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1711,7 +1811,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1740,7 +1840,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1773,7 +1873,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1802,7 +1902,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1835,7 +1935,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1864,7 +1964,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1893,7 +1993,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1922,7 +2022,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1951,7 +2051,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1980,7 +2080,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2009,7 +2109,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2038,7 +2138,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2067,7 +2167,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2096,7 +2196,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2129,7 +2229,7 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2158,7 +2258,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2191,12 +2291,16 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Report -&gt; account -&gt; journal -&gt; source reference works (trial balance rows carry drill-down parameters; ledger lines carry journal and source). Source transaction and document links arrive with each source module. Tests: tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Report -&gt; account -&gt; journal in M1; source transaction and document links arrive with each source module</t>
@@ -2226,10 +2330,14 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Closed and locked periods refuse postings (service + database); lock needs period:lock. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2253,7 +2361,7 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2282,12 +2390,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Trial balance warns about a non-zero suspense balance (account with control kind SUSPENSE). Dashboard alert is M5. Tests: tests/platform/posting-service.test.ts</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Trial balance warning in M1; dashboard alert in M5</t>
@@ -2315,7 +2427,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2344,7 +2456,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2373,14 +2485,14 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>V0 audit framework (append-only, before/after, reason, source workflow). Ledger actions are not yet audited.</t>
+          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). Source modules add their own events in M2+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -2406,12 +2518,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Positive, negative, reversal and period-lock tests exist for every M1 posting rule; the VAT test arrives with the VAT validator (M2). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Applied per rule as each milestone adds rules; the matrix lists the rule set tested</t>
@@ -2441,10 +2557,14 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Single writer enforced three ways: architecture test (only packages/accounting/src/posting.ts writes journal/journal_line/ledger_sequence; only it sets app.posting; platform/AI/worker cannot import the package), database guard (insert refused without the transaction flag), privileges. Tests: tests/unit/architecture.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Same as V1-POST-01</t>
@@ -2474,10 +2594,14 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No UPDATE/DELETE/TRUNCATE privilege for the runtime role and append-only triggers (the table owner is refused too). Tests: tests/db/ledger.test.ts, tests/db/privileges.test.ts</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Privileges, triggers, tests</t>
@@ -2507,10 +2631,14 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Reversal journals: linked both ways, mirror enforced per account at commit, at most once, a reversal cannot be reversed, dated on/after the original, in an open period. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2536,10 +2664,14 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Application validation and a deferred database check at commit. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Application and deferred database check</t>
@@ -2569,10 +2701,14 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>journal: source_type/source_id/source_reference, actor_type + posted_by_user_id, posted_at, correlation id, idempotency key; audit event and transaction.posted outbox event in the same transaction. Tests: tests/platform/posting-service.test.ts</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2596,12 +2732,16 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Journal -&gt; source via source_type/source_id/source_reference (done); source transaction -&gt; journal is delivered per source module (M2+).</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Journal -&gt; source in M1 (source_type/source_id); source -&gt; journal per module</t>
@@ -2629,7 +2769,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2662,12 +2802,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Same as V1-MOD-19</t>
@@ -2695,12 +2839,16 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Report mappings are a versioned registry (REPORT_MAPPING_VERSION = 1, returned with every account) but not yet effective-dated in the database; VAT rates are M2.</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Reporting mappings versioned in M1; VAT rates effective-dated in M2</t>
@@ -2730,10 +2878,14 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>PostingService refuses AI actors (ai_cannot_post); no journal source lists AI; architecture test forbids platform, the AI module and the worker from importing the accounting package. Tests: tests/platform/posting-service.test.ts, packages/contracts/src/ledger.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>PostingService refuses AI actors; architecture test keeps the AI module away from the posting code</t>
@@ -2761,7 +2913,7 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2790,12 +2942,16 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2.</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>TransactionPosted in M1; BankImported M4; InvoiceCreated M2</t>
@@ -2823,7 +2979,7 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2873,7 +3029,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2883,7 +3039,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2893,7 +3049,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -2953,7 +3109,7 @@
         <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -3208,7 +3208,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fae5270</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3216,7 +3220,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37923766068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V1 matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan history" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V1 matrix'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V1 matrix'!$A$1:$K$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,16 +455,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,10 +499,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Deferred scope</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -530,10 +556,30 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>account table + AccountService + /accounts API + default UK chart (UK_SMALL_COMPANY v1). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: tests/api/ledger.test.ts (chart), tests/db/ledger.test.ts (account guards), packages/contracts/src/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -553,7 +599,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -561,8 +607,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-01..05</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>A contact can hold the CUSTOMER role with payment terms, default currency, default tax treatment and credit limit; filter/search by role; company-scoped; both roles allowed; archived customers rejected on new documents.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Statements, dunning</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>V0 contacts exist (master data); customer role/terms are V1</t>
         </is>
@@ -586,7 +652,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -594,8 +660,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-01..05</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SUPPLIER role with payment terms, default expense account, bank details (field-encrypted, never in lists or logs); both roles allowed; archived suppliers rejected on new documents.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Supplier portal</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -615,7 +701,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -623,8 +709,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>M2, M3, M4, V1-MOD-02</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Invoice lifecycle DRAFT -&gt; APPROVED (posted) -&gt; paid; numbering without gaps per company; lines with VAT and currency; posting Dr receivables / Cr revenue / Cr output VAT through the PostingService with source link both ways; documents attach; AI can propose but never approve; positive, negative, reversal, VAT and period-lock tests.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Recurring invoices, quotes, online payment</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -644,7 +750,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -652,8 +758,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>M3, M4, V1-MOD-03</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Bills with VAT and currency; posting Dr expense/asset / Dr input VAT / Cr payables; duplicate-bill check; same test set as sales.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Purchase orders, expense claims</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -673,7 +799,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -681,8 +807,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-04</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>A sales credit note references its invoice (full linkage), reverses or adjusts the economic effect including VAT, cannot exceed the invoice balance, and is traceable from both documents.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Refund automation</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -702,7 +848,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -710,8 +856,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-05</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Purchase credit note / debit note with the same linkage rules against the bill.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Supplier refund workflow</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -731,7 +897,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -739,8 +905,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-04</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Receipt Dr bank / Cr receivables; allocation to one or more invoices; part payments; overpayments to an unallocated balance; realised FX difference when currencies differ.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Direct debit integration</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -760,7 +946,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -768,8 +954,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-05</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Payment Dr payables / Cr bank; allocation, part payments; realised FX difference.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Payment runs and bank file export</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -789,7 +995,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -797,8 +1003,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts as ledger accounts with bank details (field-encrypted), account currency, opening balance via M2 controls.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Open Banking feeds (V11)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -818,7 +1044,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -826,8 +1052,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounts and cash transactions with negative-cash alerts.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Petty-cash float management</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -847,7 +1093,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -855,8 +1101,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Engineering + qualified tax reviewer</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-01..15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Section 5 of v1-plan.md: all V1-VAT acceptance criteria met with verified sources.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting, Flat Rate Scheme, partial exemption, capital goods, margin schemes, OSS</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Foundation only; MTD returns are V5</t>
         </is>
@@ -890,10 +1156,30 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>POST /journals (manual and opening-balance sources), GET /journals[/id], POST /journals/{id}/reverse; all through the PostingService. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Posting only: no draft or approval step for manual journals (open decision 5 in v1-plan.md)</t>
         </is>
@@ -927,10 +1213,30 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>GET /ledger (general ledger per account, running balance, keyset paging recomputed per page). Tests: tests/platform/posting-service.test.ts (one page equals paged), tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -960,10 +1266,30 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>GET /reports/trial-balance (as at a date or a period with movement; journal lines only; balanced flag; suspense warning; drill-down parameters). Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts (independent SQL check)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -983,7 +1309,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -991,8 +1317,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>M8, trial balance</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L is computed from the trial balance via the reporting mapping, never from source transactions; every figure drills to account -&gt; journal -&gt; source -&gt; document; comparatives by period.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>FRS 102/105 layouts (V2)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1012,7 +1358,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1020,8 +1366,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>M8, trial balance</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Balance sheet from the trial balance including current-year profit; balances; drill-down as P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>FRS 102/105 layouts (V2)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1041,7 +1407,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1049,8 +1415,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Bank reconciliation states matched / partial / unmatched / suggested / manual override with audit; reconciled balance proves to the statement.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>AI suggestions (V6)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1080,10 +1466,30 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>OPEN&lt;-&gt;CLOSED-&gt;LOCKED-&gt;CLOSED with database-enforced graph, period:manage / period:lock, mandatory reasons, audit before/after, events, concurrency-safe. Tests: tests/platform/posting-service.test.ts (period controls), tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Close controls beyond 'ledger balances' are added by M2-M5 as their data exists (see MAN-ACC-08)</t>
         </is>
@@ -1117,10 +1523,30 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Source modules M5-M7</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Every source document posts through the PostingService; no module writes the ledger; each source transaction links to its journal and back.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>M1 delivers PostingService + journals + ledger with manual and reversal sources; each later milestone adds a transaction service</t>
         </is>
@@ -1154,10 +1580,30 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L and balance sheet read the trial balance only; a test fails if a report queries a source table.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>Trial balance and general ledger aggregate journal_line only (architecture: no report reads source tables). P&amp;L and balance sheet are M5. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Trial balance in M1; statements in M5, both from journal lines only</t>
         </is>
@@ -1191,10 +1637,30 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>account.code (unique per company, 1-20 chars). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1224,10 +1690,30 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>account.name. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1257,10 +1743,30 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>account.type (ASSET/LIABILITY/EQUITY/INCOME/EXPENSE). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1290,10 +1796,30 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>account.subtype (registry constrained to the type). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1323,10 +1849,30 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>account.is_control + control_kind (receivables, payables, VAT, bank, cash, suspense, retained earnings); manual journals cannot post to control accounts. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1356,10 +1902,30 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>account.tax_treatment (account level). migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Account-level treatment in M1; VAT codes on lines arrive with the VAT foundation (M2)</t>
         </is>
@@ -1393,10 +1959,30 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>account.reporting_mapping from a versioned report-line registry, checked against the type. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1426,10 +2012,30 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>account.active_from / active_to enforced on every posting date; deactivation cannot precede the last posting. migration 20260106000000_v1_ledger_core; packages/accounting; apps/api/src/ledger; ADR-44..48. Tests: packages/contracts/src/ledger.test.ts, tests/api/ledger.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1459,10 +2065,30 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>Single writer enforced three ways: architecture test (only packages/accounting/src/posting.ts writes journal/journal_line/ledger_sequence; only it sets app.posting; platform/AI/worker cannot import the package), database guard (insert refused without the transaction flag), privileges. Tests: tests/unit/architecture.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Honest limit: the flag is application-asserted (same trust boundary as tenant context)</t>
         </is>
@@ -1496,10 +2122,30 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>Application check + deferred constraint trigger at commit (header agrees with lines, contiguous numbering, reversal mirrors original). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1529,10 +2175,30 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>Accounts must exist in the company (composite FK), be active on the journal date, and not be control accounts for manual sources. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1562,10 +2228,30 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>Period must exist, contain the date and be OPEN; period row locked FOR SHARE so a concurrent close cannot race. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts (race test), tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1585,7 +2271,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1593,8 +2279,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Engineering + qualified tax reviewer</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>M4, V1-VAT-*</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>A VAT validator in the posting chain refuses a posting whose VAT treatment, rate (effective on the tax point) or amounts are inconsistent.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Validator chain exists from M1; the VAT validator ships with the VAT foundation</t>
         </is>
@@ -1618,7 +2324,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1628,10 +2334,30 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Single-currency limitation is explicit now (V1-FX-10); full multi-currency validation (transaction currency, rate, original values) delivered by M3.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>Currency validated: journals are in the company base currency and amounts respect its minor units (application + database). Foreign-currency documents, FX rates and revaluation are NOT supported (open decision 1). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Base currency of the company only; foreign-currency postings and FX revaluation are not in V1 scope until a decision is recorded</t>
         </is>
@@ -1665,10 +2391,30 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>Registered source type required; REVERSAL must name the reversed journal; other sources require a source id; idempotency key per company with content hash. Tests: tests/platform/posting-service.test.ts, packages/contracts/src/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1698,10 +2444,30 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>Source-specific permission evaluated for the journal's company through the central authoriser; AI actors refused; system actors limited to system sources. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts (roles x posting), tests/api/permissions.test.ts</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1721,7 +2487,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1729,8 +2495,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-04</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Sales example posts exactly Dr receivables / Cr revenue / Cr output VAT for standard, zero-rated and exempt lines, with tests.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1750,7 +2536,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1758,8 +2544,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-05</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Purchase example posts Dr expense or asset / Dr input VAT / Cr payables.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1779,7 +2585,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1787,8 +2593,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-08</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Receipt example Dr bank / Cr receivables.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1808,7 +2634,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -1816,8 +2642,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-09</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Payment example Dr payables / Cr bank.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1837,7 +2683,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1845,8 +2691,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>V1-MOD-06, V1-MOD-07</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Credit notes reverse or adjust the original with full source linkage in both directions.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Sales credit notes M2; purchase (debit) notes M3. The reversal primitive and source linkage ship in M1</t>
         </is>
@@ -1870,7 +2736,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -1878,8 +2744,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts created and linked to ledger accounts.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1899,7 +2785,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1907,8 +2793,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>CSV statement import as an asynchronous job with progress, retry and duplicate detection (job_record); other formats are decisions.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>OFX/MT940/Open Banking</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>Asynchronous job with progress; file formats to be decided in the M4 design</t>
         </is>
@@ -1932,7 +2838,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1940,8 +2846,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Imported transactions stored immutably with their import batch; never edited.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1961,7 +2887,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1969,8 +2895,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation workflow on transactions.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1990,7 +2936,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -1998,8 +2944,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Unmatched list with ageing and a count visible on the dashboard.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2019,7 +2985,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2027,8 +2993,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Transfers between bank accounts post one balanced journal; both statements match it.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2048,7 +3034,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2056,8 +3042,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Bank charges recognised from statements and posted to the charges account.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2077,7 +3083,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2085,8 +3091,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Interest recognised from statements and posted to interest income/expense.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2106,7 +3132,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2114,8 +3140,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Matched pairs link a statement line to ledger entries and cannot be changed without an audited un-match.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2135,7 +3181,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2143,8 +3189,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>A statement line can be matched in parts; the unmatched remainder stays visible.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2164,7 +3230,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2172,8 +3238,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Unmatched items listed with age.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2193,7 +3279,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2201,8 +3287,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Deterministic rule-based suggestions (amount, date window, reference); a suggestion never posts.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>AI suggestions (V6)</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Rule-based suggestions; AI suggestions are V6 and may only propose</t>
         </is>
@@ -2226,7 +3332,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -2234,8 +3340,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Manual matches and overrides need a reason and are audited.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2255,7 +3381,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2263,8 +3389,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Trial balance -&gt; P&amp;L / balance sheet reconcile to the cent for any period.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Trial balance in M1</t>
         </is>
@@ -2288,7 +3434,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2298,10 +3444,30 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>M5-M8</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Click-through from any report number to account -&gt; journal -&gt; source transaction -&gt; document works for every source type; a test asserts it per source.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>Report -&gt; account -&gt; journal -&gt; source reference works (trial balance rows carry drill-down parameters; ledger lines carry journal and source). Source transaction and document links arrive with each source module. Tests: tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>Report -&gt; account -&gt; journal in M1; source transaction and document links arrive with each source module</t>
         </is>
@@ -2335,10 +3501,30 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>Closed and locked periods refuse postings (service + database); lock needs period:lock. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2358,7 +3544,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2366,8 +3552,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate documents (same contact, number, date, amount) are flagged before posting; override needs a reason.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2397,10 +3603,30 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Suspense balance shown on the dashboard and blocks period lock unless acknowledged with a reason.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>Trial balance warns about a non-zero suspense balance (account with control kind SUSPENSE). Dashboard alert is M5. Tests: tests/platform/posting-service.test.ts</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>Trial balance warning in M1; dashboard alert in M5</t>
         </is>
@@ -2424,7 +3650,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2432,8 +3658,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Negative cash/bank balances alert at posting and on the dashboard.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2453,16 +3699,36 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Draft/unposted documents older than a threshold are listed and block period close unless acknowledged.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2492,10 +3758,30 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>M5-M7</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Every source module audits its actions (created, approved, posted, voided) with before/after and reason.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). Source modules add their own events in M2+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2525,10 +3811,30 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Every posting rule has positive, negative, reversal, VAT and period-lock tests; a coverage test lists the rules and fails when one lacks a category.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>Positive, negative, reversal and period-lock tests exist for every M1 posting rule; the VAT test arrives with the VAT validator (M2). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>Applied per rule as each milestone adds rules; the matrix lists the rule set tested</t>
         </is>
@@ -2562,10 +3868,30 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>Single writer enforced three ways: architecture test (only packages/accounting/src/posting.ts writes journal/journal_line/ledger_sequence; only it sets app.posting; platform/AI/worker cannot import the package), database guard (insert refused without the transaction flag), privileges. Tests: tests/unit/architecture.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>Same as V1-POST-01</t>
         </is>
@@ -2599,10 +3925,30 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
           <t>No UPDATE/DELETE/TRUNCATE privilege for the runtime role and append-only triggers (the table owner is refused too). Tests: tests/db/ledger.test.ts, tests/db/privileges.test.ts</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>Privileges, triggers, tests</t>
         </is>
@@ -2636,10 +3982,30 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
           <t>Reversal journals: linked both ways, mirror enforced per account at commit, at most once, a reversal cannot be reversed, dated on/after the original, in an open period. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2669,10 +4035,30 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>Application validation and a deferred database check at commit. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>Application and deferred database check</t>
         </is>
@@ -2706,10 +4092,30 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>journal: source_type/source_id/source_reference, actor_type + posted_by_user_id, posted_at, correlation id, idempotency key; audit event and transaction.posted outbox event in the same transaction. Tests: tests/platform/posting-service.test.ts</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2729,7 +4135,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2739,10 +4145,30 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>M5-M7</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Every source transaction type links to its journal and back; a test enumerates source types.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
           <t>Journal -&gt; source via source_type/source_id/source_reference (done); source transaction -&gt; journal is delivered per source module (M2+).</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>Journal -&gt; source in M1 (source_type/source_id); source -&gt; journal per module</t>
         </is>
@@ -2766,7 +4192,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -2774,8 +4200,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Every report number drills to ledger and source evidence.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>Same as V1-RPT-02</t>
         </is>
@@ -2809,10 +4255,30 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>M5-M7</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Close checks include unposted documents and unreconciled bank items.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>Same as V1-MOD-19</t>
         </is>
@@ -2836,7 +4302,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -2846,10 +4312,30 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
+          <t>Engineering + qualified tax reviewer</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>VAT rates and report mappings are effective-dated in the database with source and verification status; a test proves a rate change does not alter posted history.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
           <t>Report mappings are a versioned registry (REPORT_MAPPING_VERSION = 1, returned with every account) but not yet effective-dated in the database; VAT rates are M2.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>Reporting mappings versioned in M1; VAT rates effective-dated in M2</t>
         </is>
@@ -2883,10 +4369,30 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>M1 (accepted)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Met - see evidence</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
           <t>PostingService refuses AI actors (ai_cannot_post); no journal source lists AI; architecture test forbids platform, the AI module and the worker from importing the accounting package. Tests: tests/platform/posting-service.test.ts, packages/contracts/src/ledger.test.ts, tests/unit/architecture.test.ts</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>PostingService refuses AI actors; architecture test keeps the AI module away from the posting code</t>
         </is>
@@ -2910,7 +4416,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -2918,8 +4424,28 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Universal drill-down pattern available to every report.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2949,10 +4475,30 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>M5, M7</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>InvoiceCreated (M5), BankImported (M7) published through the outbox.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
           <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>TransactionPosted in M1; BankImported M4; InvoiceCreated M2</t>
         </is>
@@ -2976,7 +4522,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -2984,15 +4530,1811 @@
           <t>MISSING</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (front end)</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Usable end-to-end bookkeeping screens behind flags, tested against the real API, authorisation and tenant boundaries, with accessibility checks.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Mobile portal</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
           <t>DEC-002: parallel behind feature flags</t>
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-07</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Distinct permission `ledger:opening-balance` required for opening-balance journals</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Only holders of the permission can post OPENING_BALANCE; owner/admin/partner hold it, others do not; 403 and audited denial otherwise; role/permission sync tests pass.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-08</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Control accounts protected from ordinary manual postings; narrowly authorised adjustments need reason, evidence and audit trail</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>M1, documents/evidence links</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>A CONTROL_ADJUSTMENT request needs permission `ledger:control-adjustment`, a reason of at least 20 characters and at least one evidence document readable by the requester; posting without them fails; the journal links to the request, the evidence and the approver; ordinary MANUAL journals still cannot touch control accounts.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-09</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Configurable second-person approval for material opening balances and exceptional control-account adjustments</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (thresholds)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-07, V1-CTL-08</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Per-company policy sets the materiality threshold and which request kinds need approval; above it the journal is not posted until a different person holding `ledger:approve` approves; the requester can never approve their own request; below the threshold policy may allow direct posting only if configured; approval posts through the PostingService; rejection and expiry leave the ledger untouched.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Per-account rules; delegation; multi-step chains</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-10</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Approval requests are not ledger entries: pending requests cannot affect balances; posted journals stay immutable; correction by reversal only</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-09</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Trial balance and general ledger ignore pending requests; an approved request produces exactly one journal (idempotent); tests prove no UPDATE/DELETE path; the AI actor cannot request or approve.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-11</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>DEC-012</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Opening-balance fence replaced by permission + approval (first-day rule retained)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>V1-CTL-07</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>The first-day-of-first-period rule remains; a test shows the permission, approval and date rule all apply together.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-01</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional currency: company base currency is the functional currency; cannot change once postings exist</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>A company has exactly one functional currency; changing it after the first posting is refused by the database; documented.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-02</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Transaction currency on documents and journal lines (ISO 4217 from the currency table)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-01</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>A line carries its transaction currency; only known, active currencies accepted; functional-currency lines need no rate.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-03</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Exchange-rate source and date: rates stored with source, rate date, provenance and verification status; lookup rule documented</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (source decision)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Open decision: rate source</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Rate table with (from, to, date, rate, source, retrieved_at, verified); manual entry audited; a documented lookup rule (transaction date, else last earlier rate within N days, else refuse); an unverified rate is flagged and can be blocked by policy; a rate-source adapter port exists with a fake for tests; no live source is enabled without a recorded decision.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-04</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Original-currency values preserved on every foreign-currency line (amount, currency, rate, rate id) and immutable</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-02, V1-FX-03</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Journal lines store original amount, currency and the rate used; a reversal reproduces them; the ledger refuses lines with an original amount but no rate and vice versa.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-05</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional-currency postings: journals balance in the functional currency and per currency; rounding differences to a designated rounding account</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-04</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>For every journal sum(debit)=sum(credit) in functional currency; a conversion that does not round cleanly produces an explicit rounding line to a system rounding account, capped by a tolerance; tests with awkward rates.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-06</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Rounding rules: rate precision, per-line vs per-document conversion, rounding mode, minor units per currency</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (policy)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Open decision: rounding policy</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>The policy is written (precision, mode, level), implemented in one function and covered by property tests (conversion then reverse conversion within tolerance; totals independent of line order).</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-07</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Realised FX gains and losses on settlement (receipts/payments against invoices/bills)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-05, M5, M6</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Settling a foreign invoice at a different rate posts the difference to realised gain/loss accounts exactly once; partial settlements prorate; tested with several rates.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Engine in M3; used by receipts and payments in M5/M6</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-08</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Period-end revaluation of monetary items (unrealised) with auto-reversal</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (policy)</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-05, open decision: revaluation policy</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Revaluation at period end posts unrealised gain/loss journals for foreign-currency receivables, payables and bank, and reverses on the first day of the next period; idempotent per period; blocked in locked periods; reconciles to the sub-ledger.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-09</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Acceptance tests for reconciliation and reporting in multiple currencies</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-05..08</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Trial balance in functional currency balances; the sub-ledger in original currency revalued at the closing rate equals the control account; FX gain/loss report drills to journals.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Multi-currency reporting checks repeat in M8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>V1-FX-10</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>DEC-009</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Single-currency limitation is explicit until the foundation is implemented</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>A journal request naming a currency other than the company base currency is refused with code `foreign_currency_not_supported` and a message pointing to the plan; OpenAPI and documentation state the limitation; tests cover it.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Delivered with this plan update: PostingService refuses a non-base `currency` with `foreign_currency_not_supported`; OpenAPI description on POST journals; v1-plan.md section 4. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts, packages/contracts/src/ledger.test.ts.</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-01</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Effective-dated tax codes (code, treatment, direction, description) with source and verification status</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-02</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Effective-dated rates per tax code (no overlapping rates for one code), each with official source reference, retrieval date and UNVERIFIED/VERIFIED status; an UNVERIFIED rate cannot be activated</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-03</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Treatments: standard, reduced, zero-rated, exempt, outside the scope of VAT</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-04</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Sales VAT (output tax) on invoices; purchase VAT (input tax) on bills</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-05</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>VAT on credit notes and debit notes with linkage to the original supply</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-06</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>VAT-inclusive and VAT-exclusive entry; calculations exact, rounding rule documented and tested</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-07</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Tax-point handling: supply date, invoice date, payment date; the rate and period are those of the tax point</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-08</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Control-account reconciliation: the VAT control account equals the sum of VAT lines by period; breaks are listed</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-09</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>VAT-return workpaper (the nine-box figures with drill-down to transactions) - a workpaper, not a submission</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-10</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Reverse-charge cases accommodated by the model (e.g. domestic reverse charge, imported services): a line can account for output and input VAT simultaneously</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-11</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>VAT treatment/rate is separate from VAT accounting scheme; scheme registry with STANDARD active and CASH / FLAT_RATE present but not implemented and not selectable</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-12</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Every tax rule records its official HMRC source, effective dates and who verified it; nothing is entered from memory</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-13</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>VAT registration details on the company (number, effective date, return frequency, scheme) with validation</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Posting validator enforces consistency of treatment, rate and amounts (V1-POST-05)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>V1-VAT-15</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>DEC-010</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Foreign-currency VAT: VAT amounts in the functional currency per the verified rule, with the original-currency amounts kept</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); qualified tax reviewer (rules)</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>M3; verified HMRC sources</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with tests: positive, negative, reversal, period-lock and effective-date boundary cases; sources verified and recorded before activation.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-01</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>DEC-011</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Customer and supplier roles on the shared `contact`, with role-specific profile tables for differing fields</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>V0 contacts (master data), V0 field encryption</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with API, permission, tenant-isolation and audit tests.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Contact merge; import from other systems (V11)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-02</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>DEC-011</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>One contact may hold both roles; roles are added and removed with audit; removing a role is refused while open documents exist</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>V0 contacts (master data), V0 field encryption</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with API, permission, tenant-isolation and audit tests.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Contact merge; import from other systems (V11)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-03</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>DEC-011</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Tenant and company scope enforced on roles and profiles (a company-level contact is invisible to other companies)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>V0 contacts (master data), V0 field encryption</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with API, permission, tenant-isolation and audit tests.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Contact merge; import from other systems (V11)</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-04</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>DEC-011</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Documents keep a snapshot of the contact details used (name, address, VAT number) so history survives later edits</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>V0 contacts (master data), V0 field encryption</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with API, permission, tenant-isolation and audit tests.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Contact merge; import from other systems (V11)</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>V1-CON-05</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>DEC-011</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Sensitive profile data (bank details) encrypted at field level and never returned in lists, logs or audit snapshots</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>V0 contacts (master data), V0 field encryption</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Meets the requirement with API, permission, tenant-isolation and audit tests.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Contact merge; import from other systems (V11)</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>V1-PRIV-01</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>DEC-013</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Session/challenge IP and user agent: collection, use, access and purpose traced; policy-controlled retention and deletion proposed; tests</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Privacy track (parallel to V1)</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (investigation); DPO / legal (review and decisions)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>V0 audit switch; retention schedule (DEC-003)</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>docs/legal/device-metadata-investigation.md traces every write and read with code references; characterisation tests fail if collection or exposure changes silently; a proposal for policy-controlled retention/deletion is written but NOT enabled; the item is not marked resolved until the privacy review is recorded.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Any deletion job (S4(b) is frozen)</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G78"/>
+  <autoFilter ref="A1:K114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3003,7 +6345,509 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Deferred scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ledger core: chart of accounts, period states, PostingService, journals, general ledger, trial balance</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPTED (code baseline fae5270; DEC-008)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>v1-m1-acceptance.md</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Foreign currency (M3), VAT (M4), source documents (M5+), UI (M9)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ledger controls: opening-balance permission, control-account adjustments, configurable second-person approval (DEC-012)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SPECIFIED - ready to start</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (approval thresholds, who may approve)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>M1 accepted; V0 notification channel port (S2, delivered) for approver notifications; V0 documents + evidence links for supporting evidence</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Section 3 of v1-plan.md; the M2 acceptance package (DEC-007)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Per-account approval rules and delegation; AI-assisted review (V6/V8); workflow-engine integration for multi-step approval</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Foreign-currency foundation: functional/transaction currency, rates, original-currency values, rounding, realised FX, revaluation (DEC-009)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SPECIFIED - open decisions block the start (exchange-rate source, rounding policy)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner (rate source, policies)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>M1 accepted; M2 not required; Decision: exchange-rate source and revaluation policy (v1-plan.md section 4)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Section 4 of v1-plan.md</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Hedge accounting, forward contracts, multi-currency bank feeds (M7 handles statements in account currency only), intercompany eliminations</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Contact roles (customer/supplier) and VAT foundation - standard VAT accounting (DEC-010, DEC-011)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SPECIFIED - external gate: HMRC rules must be verified from official sources before activation</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (build); product owner + qualified tax reviewer (rule verification)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>M1 accepted; M3 delivered (VAT flows are finalised after FX); Verified HMRC sources recorded per rule</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Section 5 of v1-plan.md</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Cash accounting scheme, Flat Rate Scheme, partial exemption, capital goods scheme, margin schemes, OSS/import schemes, MTD submission (V5)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sales: invoices, credit notes, receipts; duplicate-document check</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PLANNED - specification after M3/M4 design</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>M2; M3; M4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>To be written when the milestone is specified</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Recurring invoices, quotes, online payments, customer statements beyond the ledger view</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Purchases: bills, debit notes, payments, cash</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>M5 patterns; M3; M4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>To be written when the milestone is specified</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Payment runs, expense claims, purchase orders</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts, statement import (async), transfers, charges, interest, reconciliation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>M5; M6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>To be written when the milestone is specified</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Open Banking and bank feeds (V11), AI match suggestions (V6)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Profit and loss, balance sheet, drill-down to documents, controls and alerts, FX reporting</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>M3; M5; M6; M7</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>To be written when the milestone is specified</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>FRS 102/105 statements (V2), comparatives and notes (V2)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>V1 UI slices behind feature flags (DEC-002)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PLANNED - runs in parallel from M2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (front end)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>API of the milestone each screen uses</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Per screen: works against the real API, authorisation and tenant boundaries; accessibility checks</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mobile client portal (V7)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Privacy track (parallel to V1)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Privacy finding on session / challenge IP and user agent (DEC-013)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>INVESTIGATION IN PROGRESS - never marked resolved without review</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Engineering (investigation); DPO / legal (decisions)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>DEC-003 retention review</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>V1-PRIV-01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Any purge or deletion enabling (S4(b) frozen)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3029,7 +6873,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -3049,7 +6893,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -3069,172 +6913,90 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
+          <t>Plan version</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>Commit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ledger core: chart of accounts, period states, PostingService, journals, general ledger, trial balance</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>34</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26</v>
+          <t>fae5270</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Contacts as customers/suppliers, VAT foundation, sales, credit notes, receipts</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37923766068</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>Generated</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purchases, debit notes, payments, cash</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bank accounts, statement import, transfers, charges, interest, reconciliation</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Profit and loss, balance sheet, drill-down to documents, controls and alerts</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>V1 UI slices behind feature flags (DEC-002)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fae5270</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37923766068</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Generated</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="160" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v1 (2026-10-09): 77 rows, milestones M1-M6 (initial plan, commit 0aeff94 lineage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-09, DEC-008..014): M1 accepted (fae5270). Milestones re-sequenced: new M2 (ledger controls), M3 (foreign currency), M4 (contact roles + VAT foundation); old M2 -&gt; M5 (sales) + M4 (VAT/customers), old M3 -&gt; M6, old M4 -&gt; M7, old M5 -&gt; M8, old M6 -&gt; M9. Rows added: V1-FX-*, V1-VAT-*, V1-CON-*, V1-CTL-07..11, V1-PRIV-01. Each row now carries owner, dependencies, acceptance criteria and deferred scope.</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6305,9 +6305,9 @@
           <t>Privacy track (parallel to V1)</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -6330,8 +6330,16 @@
           <t>Any deletion job (S4(b) is frozen)</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Investigation delivered: docs/legal/device-metadata-investigation.md (7 collection points traced, 6 findings F-1..F-6, options A-F proposed and NOT enabled, review checklist); 10 characterisation tests in tests/api/device-metadata.test.ts; legal schedule corrected (raw IPs in Redis rate-limit keys). The finding is UNRESOLVED: no policy, deletion or lawful basis is approved; deletion stays frozen (S4(b)).</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Never mark resolved without the recorded privacy review</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K114"/>
@@ -6806,7 +6814,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>INVESTIGATION IN PROGRESS - never marked resolved without review</t>
+          <t>INVESTIGATION DELIVERED - finding UNRESOLVED, awaiting privacy review (never resolved without it)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6883,7 +6891,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -6893,7 +6901,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -3778,7 +3778,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). Source modules add their own events in M2+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
+          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). M2 adds ledger.request_created/approved/rejected/cancelled and ledger.policy_changed (before/after, reason). Source modules add their own events in M5+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
@@ -4578,9 +4578,9 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4603,7 +4603,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Permission `ledger:opening-balance` (COMPANY scope) is required to request an opening balance; owner/admin/partner hold it, manager/accountant/bookkeeper/reviewer/client viewer do not (migration 20260107000000 + role sync). `journal:post` alone no longer suffices; `POST /journals` refuses OPENING_BALANCE. Tests: tests/api/ledger-controls.test.ts (permission matrix over 8 roles for all four new permissions, 22 cases), tests/api/permissions.test.ts (4 new probes x 8 roles), packages/contracts/src/ledger.test.ts</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
@@ -4627,9 +4631,9 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4652,7 +4656,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL_ADJUSTMENT request needs `ledger:control-adjustment` (accountant, owner/admin/partner), a reason of at least 20 characters (service + database check), at least one evidence document that exists, belongs to the company and is readable by the requester (restricted documents indistinguishable from missing), and must touch a control account. The journal records request, requester and approver and the evidence is linked journal -&gt; document in the evidence graph; MANUAL journals still refused on control accounts. Tests: tests/api/ledger-controls.test.ts (validation, control-account adjustment, evidence graph), tests/platform/posting-service.test.ts</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4676,9 +4684,9 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4701,7 +4709,11 @@
           <t>Per-account rules; delegation; multi-step chains</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Per-company `ledger_policy` (ALWAYS default / ABOVE_THRESHOLD with strictly-greater materiality threshold, expiry 1-90 days; no NEVER mode - database check). Above the threshold a different person holding `ledger:approve` must approve; requester can never approve (service + database, tested against the table owner path). Below-threshold direct posting only when configured, recorded as self-approved; reject (reason required), cancel (requester only) and expiry leave the ledger untouched. Policy changes need `ledger:policy` + reason and are audited before/after. Tests: tests/api/ledger-controls.test.ts (policy, threshold boundary 1000.00 / 1000.01, concurrency), tests/db/ledger-controls.test.ts (13), tests/platform/ledger-requests.test.ts (5)</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
@@ -4725,9 +4737,9 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4750,7 +4762,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Pending requests live in `journal_request` and are never read by trial balance / general ledger (asserted). An approved request produces exactly one journal (unique `journal.request_id`; idempotency key `request:&lt;id&gt;`; concurrent approvals and approve/reject/cancel races end with one outcome). Posted journals stay immutable and are corrected by reversal (tested); AI actors cannot request, approve or post (service + PostingService). Request content is immutable and decided requests final (trigger); no delete/truncate for runtime role or owner. Tests: tests/api/ledger-controls.test.ts, tests/db/ledger-controls.test.ts, tests/platform/ledger-requests.test.ts, tests/db/privileges.test.ts, tests/unit/architecture.test.ts (single writer of journal_request/ledger_policy)</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
@@ -4774,9 +4790,9 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4799,7 +4815,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>The first-day-of-first-period rule is kept (validated at request creation and again at posting) together with the dedicated permission and the approval policy; a request dated elsewhere is refused with `opening_balance_date_invalid`. Tests: tests/api/ledger-controls.test.ts (validation), tests/platform/posting-service.test.ts</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
@@ -6470,7 +6490,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SPECIFIED - ready to start</t>
+          <t>IMPLEMENTED - submitted for acceptance (see v1-m2-acceptance.md for the commit, CI run and results)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6497,7 +6517,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6881,7 +6901,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6901,7 +6921,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -6942,7 +6962,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fae5270</t>
+          <t>d98e3ed</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6974,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37923766068</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37933029493</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7008,6 +7028,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2.1 (2026-10-09): M2 ledger controls implemented. V1-CTL-07..11 -&gt; Implemented with evidence; V1-CTL-06 evidence extended. No rows added or removed; M3+ unchanged and still gated. Not accepted until the product owner says so.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -4865,7 +4865,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -4953,21 +4953,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Open decision: rate source</t>
+          <t>DEC-016</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Rate table with (from, to, date, rate, source, retrieved_at, verified); manual entry audited; a documented lookup rule (transaction date, else last earlier rate within N days, else refuse); an unverified rate is flagged and can be blocked by policy; a rate-source adapter port exists with a fake for tests; no live source is enabled without a recorded decision.</t>
+          <t>`exchange_rate` table (kind DAILY|PERIOD, rate to 8 dp, publisher, series, URL, retrieved_at, source_kind MANUAL|IMPORT, verification status, supersedes); manual entry needs source text and date and is audited; rows are immutable (corrections supersede); lookup = transaction date, else latest earlier DAILY rate within 7 days, else `exchange_rate_not_found`, never a future rate; CSV importer + `ExchangeRateSource` port with a fake; UNVERIFIED rates flagged and blockable by `ledger_policy.fx_block_unverified_rates`; live HTTP adapters NOT included (gate).</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Decision DEC-016 applied.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5012,7 +5016,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
@@ -5056,12 +5060,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>For every journal sum(debit)=sum(credit) in functional currency; a conversion that does not round cleanly produces an explicit rounding line to a system rounding account, capped by a tolerance; tests with awkward rates.</t>
+          <t>For every journal sum(debit)=sum(credit) in functional currency; unbalanced converted lines get one visible FX-rounding line on the system account `FX_ROUNDING`, permitted difference one minor unit per line, else `rounding_tolerance_exceeded`; tests for within/beyond tolerance.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
@@ -5100,21 +5104,25 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Open decision: rounding policy</t>
+          <t>DEC-017</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>The policy is written (precision, mode, level), implemented in one function and covered by property tests (conversion then reverse conversion within tolerance; totals independent of line order).</t>
+          <t>Rate stored to 8 dp unrounded; functional amount rounded per line, half-up, to the functional currency's minor units by one function with property tests (reverse conversion within tolerance; totals independent of line order; half-up boundary); VAT rounding left to M4.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Decision DEC-017 applied.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5154,18 +5162,18 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Settling a foreign invoice at a different rate posts the difference to realised gain/loss accounts exactly once; partial settlements prorate; tested with several rates.</t>
+          <t>`FxService.settle` posts the difference between the functional value carried and the value at the settlement rate to `FX_REALISED` exactly once; partial settlements prorate; tested with several rates (receipts/payments in M5/M6 call it).</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Engine in M3; used by receipts and payments in M5/M6</t>
+          <t>Engine in M3; used by receipts and payments in M5/M6 Decision DEC-018 applied.</t>
         </is>
       </c>
     </row>
@@ -5202,21 +5210,25 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>V1-FX-05, open decision: revaluation policy</t>
+          <t>V1-FX-05, DEC-018</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Revaluation at period end posts unrealised gain/loss journals for foreign-currency receivables, payables and bank, and reverses on the first day of the next period; idempotent per period; blocked in locked periods; reconciles to the sub-ledger.</t>
+          <t>Explicit, previewed `revalue` action (`period:manage`) per period revalues foreign-currency monetary accounts at the period-end rate to `FX_UNREALISED`; auto-reversal dated the first day of the next period (immediately or by sweeper); idempotent per period via `fx_revaluation_run`; refused in locked periods; close needs acknowledgement if a balance is unrevalued; non-monetary items untouched.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Decision DEC-018 applied.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5261,7 +5273,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting; forward contracts; intercompany eliminations</t>
+          <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -6490,7 +6502,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED - submitted for acceptance (see v1-m2-acceptance.md for the commit, CI run and results)</t>
+          <t>ACCEPTED (code baseline d98e3ed; DEC-015)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6533,7 +6545,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SPECIFIED - open decisions block the start (exchange-rate source, rounding policy)</t>
+          <t>SPECIFIED - decisions recorded (DEC-016..018); ready to start; live rate adapters gated</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6543,17 +6555,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>M1 accepted; M2 not required; Decision: exchange-rate source and revaluation policy (v1-plan.md section 4)</t>
+          <t>M1 accepted; M2 accepted (DEC-015); Decisions recorded: rate source and window (DEC-016), rounding (DEC-017), revaluation and realised FX (DEC-018)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Section 4 of v1-plan.md</t>
+          <t>Section 5 of v1-plan.md (5.3)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Hedge accounting, forward contracts, multi-currency bank feeds (M7 handles statements in account currency only), intercompany eliminations</t>
+          <t>Live HTTP rate adapters (network, publisher terms of use and format verification), hedge accounting, forward contracts, net investments and translation of foreign operations, intercompany eliminations, multi-currency bank statements beyond the account currency (M7), VAT-specific rate rules (M4)</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -6986,7 +6998,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7035,6 +7047,13 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v2.2 (2026-10-12, DEC-015..018): M2 ACCEPTED (code baseline d98e3ed). M3 decisions recorded (rate source and window, rounding, revaluation/realised FX); M3 specification completed in v1-plan.md section 5 and ready to start. No rows added or removed. M4 remains gated by verification of tax rules from official sources.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -4843,9 +4843,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4868,7 +4868,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Functional currency = `company.base_currency`; a database trigger refuses a change once the company has any journal (before the first journal it can change). Tests: tests/db/fx.test.ts (base currency), tests/platform/fx.test.ts</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
@@ -4892,9 +4896,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4917,7 +4921,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Transaction currency must exist in the `currency` table (`unknown_currency` otherwise); original amounts respect that currency's own minor units (service and database, e.g. yen has none). Tests: tests/platform/fx.test.ts (validation), tests/db/fx.test.ts (minor units)</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4941,9 +4949,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4966,7 +4974,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>`exchange_rate`: kind DAILY|PERIOD, 8-dp rate never rounded, MANUAL (source text mandatory, audited) or IMPORT (CSV file with publisher, series, URL, retrieved-at, batch), UNVERIFIED/VERIFIED (second person), immutable with supersession. Lookup: transaction date, else latest earlier DAILY rate within 7 days, else `exchange_rate_not_found`, never a later rate; ambiguity between series resolved by the company's default series; `fx_block_unverified_rates` policy. Live HTTP adapters are NOT included (gate). Tests: tests/platform/fx.test.ts (window boundaries day 0/+7/+8/-1, weekend, PERIOD, ambiguity, supersession, verification, import), tests/db/fx.test.ts, tests/api/fx.test.ts, tests/unit/fx-math.test.ts</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
           <t>Decision DEC-016 applied.</t>
@@ -4994,9 +5006,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5019,7 +5031,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>`journal_line` stores original currency, original debit/credit, rate and rate id (all-or-none); immutable (ledger triggers); a reversal copies them with sides swapped; the line guard rejects a rate that is not the stored rate for the pair, a rate dated after the journal, a wrong side. Tests: tests/db/fx.test.ts, tests/platform/fx.test.ts (reversal), tests/api/fx.test.ts</t>
+        </is>
+      </c>
       <c r="K87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
@@ -5043,9 +5059,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5068,7 +5084,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Foreign journals are converted per line and balanced in the functional currency; a visible system line on the designated FX-rounding account absorbs a difference of up to one minor unit per line (`rounding_tolerance_exceeded` beyond; `fx_rounding_account_missing` if unset); the foreign-currency amounts must balance too. Tests: tests/platform/fx.test.ts (rounding line 24.72 example), tests/unit/fx-math.test.ts (tolerance property), tests/db/fx.test.ts</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
@@ -5092,9 +5112,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5117,7 +5137,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>One `convert` function: rate x original rounded half-up to the functional minor units; rates stored to 8 dp; VAT rounding left to M4. Property-style tests: boundary (0.125 -&gt; 0.13), minor units 0/2/3, reverse conversion within tolerance, totals independent of line order; database re-proves with `round()`. Tests: tests/unit/fx-math.test.ts, tests/db/fx.test.ts</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
           <t>Decision DEC-017 applied.</t>
@@ -5145,9 +5169,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5170,7 +5194,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts</t>
+        </is>
+      </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>Engine in M3; used by receipts and payments in M5/M6 Decision DEC-018 applied.</t>
@@ -5198,9 +5226,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -5223,7 +5251,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Explicit, previewed revaluation per period (`period:manage`) of foreign-currency monetary accounts (by subtype) at the closing rate to the designated unrealised account; one journal (source FX_REVALUATION) and an auto-reversal on the next day (at once if that period is open, otherwise due and blocking close of the period containing its date); idempotent by carrying-amount comparison; concurrent runs post one journal; refused in closed/locked periods; non-monetary and P&amp;L accounts untouched; close without revaluation needs `acknowledgeUnrevaluedFx`. Tests: tests/platform/fx.test.ts (revaluation, close controls, concurrency), tests/api/fx.test.ts</t>
+        </is>
+      </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
           <t>Decision DEC-018 applied.</t>
@@ -5251,9 +5283,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5276,7 +5308,11 @@
           <t>Live rate adapters (gated); hedge accounting; forward contracts; net investments; intercompany eliminations</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation proven: after revaluation, original balance x closing rate equals the functional carrying amount per account (tests/platform/fx.test.ts); the functional-currency trial balance balances and the FX accounts' general ledger drills to the revaluation journal and its reversal (tests/api/fx.test.ts). A dedicated FX gain/loss report and multi-currency statements belong with reporting (M8).</t>
+        </is>
+      </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
           <t>Multi-currency reporting checks repeat in M8</t>
@@ -5331,7 +5367,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Delivered with this plan update: PostingService refuses a non-base `currency` with `foreign_currency_not_supported`; OpenAPI description on POST journals; v1-plan.md section 4. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts, packages/contracts/src/ledger.test.ts.</t>
+          <t>Superseded in part by M3: foreign-currency journals are now converted. The limitation that remains is explicit: opening balances and control adjustments are posted in the company currency only (`foreign_currency_not_supported`, message and OpenAPI updated). Tests: tests/api/ledger-controls.test.ts, tests/platform/fx.test.ts</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -6545,7 +6581,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SPECIFIED - decisions recorded (DEC-016..018); ready to start; live rate adapters gated</t>
+          <t>IMPLEMENTED - submitted for acceptance (see v1-m3-acceptance.md for the commit, CI run and results)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6572,7 +6608,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -6913,7 +6949,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -6923,7 +6959,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -6933,7 +6969,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -6974,7 +7010,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>d98e3ed</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -6984,11 +7020,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/37933029493</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7013,7 +7045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7054,6 +7086,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v2.3 (2026-10-12): M3 foreign-currency foundation implemented. V1-FX-01..06, 08, 10 -&gt; Implemented; V1-FX-07 and V1-FX-09 stay Partially implemented (settlement path needs M5/M6; FX report is M8). No rows added or removed. Not accepted until the product owner says so.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>c8fd8c0</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38265470095</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6128,9 +6128,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -6153,7 +6153,11 @@
           <t>Contact merge; import from other systems (V11)</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>`contact_role` (CUSTOMER/SUPPLIER per company) with `customer_profile` (terms, credit limit, default currency) and `supplier_profile` (terms, default currency, default expense account, bank details); the database ties each profile to a role of the right kind and company. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts</t>
+        </is>
+      </c>
       <c r="K109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
@@ -6177,9 +6181,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6202,7 +6206,11 @@
           <t>Contact merge; import from other systems (V11)</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts</t>
+        </is>
+      </c>
       <c r="K110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
@@ -6226,9 +6234,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -6251,7 +6259,11 @@
           <t>Contact merge; import from other systems (V11)</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Roles and profiles are company-scoped (path permission per company, forced RLS per organisation); a company-linked contact cannot take a role in another company (service and database trigger); another company's path returns 404; another organisation sees zero rows. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts</t>
+        </is>
+      </c>
       <c r="K111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
@@ -6275,9 +6287,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6300,7 +6312,11 @@
           <t>Contact merge; import from other systems (V11)</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>The snapshot function (name, kind, VAT number, account code, primary address, capture time) is delivered and tested; storing it on documents and proving history survives an edit after issue needs documents (M5/M6). Tests: tests/api/contact-roles.test.ts</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
@@ -6324,9 +6340,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -6349,7 +6365,11 @@
           <t>Contact merge; import from other systems (V11)</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Supplier bank details are AES-256-GCM field-encrypted (AAD = role id); the database refuses plain digits; lists, the role view and audit records carry only a mask; full details only via GET bank-details with `contact:bank-details`, each read audited; a change resets to UNVERIFIED and must be verified by a different person (service and database check). Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts, tests/unit/architecture.test.ts (single writer, ciphertext touched only by the role service)</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
@@ -6581,7 +6601,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IMPLEMENTED - submitted for acceptance (see v1-m3-acceptance.md for the commit, CI run and results)</t>
+          <t>ACCEPTED under delegation (code baseline c8fd8c0; DEC-019)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6619,12 +6639,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Contact roles (customer/supplier) and VAT foundation - standard VAT accounting (DEC-010, DEC-011)</t>
+          <t>M4a contact roles (customer/supplier, DEC-011, DEC-023) and M4b VAT foundation - standard VAT accounting (DEC-010, DEC-021)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SPECIFIED - external gate: HMRC rules must be verified from official sources before activation</t>
+          <t>M4a IMPLEMENTED - see v1-m4a-acceptance.md; M4b SPECIFIED (build allowed; activation of VAT rules gated by verification under DEC-021/022)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6634,12 +6654,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>M1 accepted; M3 delivered (VAT flows are finalised after FX); Verified HMRC sources recorded per rule</t>
+          <t>M1-M3 accepted (DEC-008, DEC-015, DEC-019); M4b: verification of each VAT rule by a holder of tax:rule-verify (DEC-021); primary sources not readable in this sandbox (DEC-022)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Section 5 of v1-plan.md</t>
+          <t>v1-plan.md section 6 (6.1 contact roles, 6.2 VAT); M4a package v1-m4a-acceptance.md</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6651,7 +6671,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6949,7 +6969,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -6959,7 +6979,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -6969,7 +6989,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -7010,7 +7030,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c8fd8c0</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7020,11 +7040,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38265470095</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7049,7 +7065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7097,6 +7113,13 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v2.4 (2026-10-12, DEC-019..024 under delegated authority): M3 accepted; M4 split into M4a (contact roles, implemented) and M4b (VAT). V1-CON-01, -03, -05 -&gt; Implemented; V1-CON-02 and -04 Partially implemented (need documents, M5/M6). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -2274,9 +2274,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2299,7 +2299,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>VAT validation in the posting chain (see V1-VAT-14). Tests: tests/platform/vat.test.ts, tests/db/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Validator chain exists from M1; the VAT validator ships with the VAT foundation</t>
@@ -5393,9 +5397,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5418,7 +5422,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>`tax_code` (code, name, treatment, direction, reverse charge; immutable; unique per organisation); verification status lives on each rate version. Tests: tests/db/vat.test.ts, tests/platform/vat.test.ts, tests/api/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
@@ -5442,9 +5450,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5467,7 +5475,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>`tax_rate` versions: effective-dated, no overlap among current versions of a code (trigger), official source URL + provision + retrieval date mandatory, box mapping; changed only by supersession (UNVERIFIED again). Tests: tests/db/vat.test.ts, tests/platform/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
@@ -5491,9 +5503,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5516,7 +5528,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>STANDARD, REDUCED (rate &gt; 0) and ZERO, EXEMPT, OUTSIDE_SCOPE (rate 0) enforced by the database; zero/exempt/outside lines carry their code with no VAT line; outside scope maps to no box. Tests: tests/platform/vat.test.ts, tests/db/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
@@ -5540,9 +5556,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5565,7 +5581,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Output VAT (sales codes) and input VAT (purchase codes) on journal lines, with visible VAT lines on the configured accounts. Invoices and bills are documents (M5/M6), so 'on invoices/bills' is not yet possible. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
@@ -5589,9 +5609,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5614,7 +5634,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>A credit note entered as a debit on a sales code reduces output VAT (tested); linkage to the original supply needs documents (M5/M6).</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
@@ -5638,9 +5662,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5663,7 +5687,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive (round(net x r/100)) and inclusive (round(gross x r/(100+r))) entry, per line half-up (DEC-025; rule UNVERIFIED vs HMRC); the database re-proves each VAT line at commit. Tests: tests/unit/vat-math.test.ts (boundaries, net+VAT = gross), tests/db/vat.test.ts, tests/platform/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
@@ -5687,9 +5715,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5712,7 +5740,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Explicit tax point per journal (defaults to the journal date) selects the rate version and the return period (stagger function tested). Determining it from supply/invoice/payment dates is a document matter (M5/M6). Tests: tests/platform/vat.test.ts, tests/unit/vat-math.test.ts</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
@@ -5736,9 +5768,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5761,7 +5793,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Workpaper reconciliation: movement on the VAT accounts by journal date versus VAT lines by tax point, difference listed with the entries that explain it (non-VAT postings, tax points outside the journal's period). Tests: tests/platform/vat.test.ts (hand-calculated -9.50 example), tests/api/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
@@ -5785,9 +5821,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5810,7 +5846,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Nine-box workpaper by tax point with drill-down per box, the verified rules used (source and verifier) and an explicit 'not a return, not a submission' notice. Tests: tests/platform/vat.test.ts (all boxes against a hand-calculated synthetic scenario), tests/api/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
@@ -5834,9 +5874,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5859,7 +5899,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Reverse-charge purchase codes post equal output and input VAT lines (RC_OUTPUT/RC_INPUT) proven equal by the database; the applicable cases are whatever verified rule versions the firm defines. Tests: tests/platform/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
@@ -5883,9 +5927,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5908,7 +5952,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Scheme registry (STANDARD implemented; CASH and FLAT_RATE registered, refused by the service and by a database check); codes and rates never encode the scheme. Tests: tests/platform/vat.test.ts, tests/db/vat.test.ts, tests/api/vat.test.ts, tests/unit/vat-math.test.ts</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
@@ -5932,9 +5980,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5957,7 +6005,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Every rate version records source URL, provision and retrieval date, and who verified it, when, with notes (optionally an evidence document); verification is by a holder of `tax:rule-verify` other than the author (service and database); nothing is seeded. **The rules themselves are verified by the firm, not by this platform.** Tests: tests/db/vat.test.ts, tests/platform/vat.test.ts, tests/api/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
@@ -5981,9 +6033,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6006,7 +6058,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Company VAT settings: registration, VRN (format), registration date, scheme, period length and stagger (month-end), output and input VAT accounts; audited with reason; VAT codes refused before registration. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts, tests/unit/vat-math.test.ts</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
@@ -6030,9 +6086,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -6055,7 +6111,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>PostingService VAT step plus the commit-time database proof (verified, current version of the line's code, covering the tax point; exact VAT amount; reverse-charge pair equal). Tests: tests/db/vat.test.ts, tests/platform/vat.test.ts</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
@@ -6104,7 +6164,11 @@
           <t>Cash accounting; Flat Rate Scheme; partial exemption; capital goods scheme; margin schemes; OSS/import schemes; MTD submission (V5)</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Not implemented by design: VAT on foreign-currency journals is refused (`vat_foreign_currency_not_supported`, service and database) until the rule on the currency of VAT amounts is verified.</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
@@ -6644,7 +6708,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>M4a IMPLEMENTED - see v1-m4a-acceptance.md; M4b SPECIFIED (build allowed; activation of VAT rules gated by verification under DEC-021/022)</t>
+          <t>M4a VERIFIED (code baseline 206b14d; v1-m4a-acceptance.md); M4b IMPLEMENTED - see v1-m4b-acceptance.md. Every VAT rule is usable only after verification by the firm's holder of tax:rule-verify</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6671,7 +6735,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -6969,7 +7033,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -6979,7 +7043,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -6989,7 +7053,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -7065,7 +7129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7120,6 +7184,13 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v2.5 (2026-10-12, DEC-025): M4b VAT foundation implemented. V1-VAT-01, -02, -03, -06, -08..14 and V1-POST-05 -&gt; Implemented; V1-VAT-04, -05, -07 Partially implemented (documents M5/M6); V1-VAT-15 stays Missing by design. No rule figures seeded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>M4a VERIFIED (code baseline 206b14d; v1-m4a-acceptance.md); M4b IMPLEMENTED - see v1-m4b-acceptance.md. Every VAT rule is usable only after verification by the firm's holder of tax:rule-verify</t>
+          <t>M4a VERIFIED (206b14d; v1-m4a-acceptance.md); M4b VERIFIED (6fb1938; v1-m4b-acceptance.md). VAT rules usable only after verification by the firm's holder of tax:rule-verify</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>6fb1938</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38311897860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -704,9 +704,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -729,8 +729,16 @@
           <t>Recurring invoices, quotes, online payment</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Invoices: DRAFT (no number, no ledger effect; revisioned lines) -&gt; APPROVED (numbered without gaps from a locked sequence the database checks; customer snapshot; amounts recomputed with verified VAT rates; posted as SALES_INVOICE Dr receivables / Cr revenue / Cr output VAT; journal and document linked both ways; immutable) or DISCARDED; attachments through the evidence graph; drafts from ACCEPTED AI proposals, approval by people only; positive, negative, VAT (standard, zero, exempt; exclusive, inclusive), period-lock and correction-by-credit-note tests. 'Paid' is reached by credit notes now; by receipts in M5b. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>M5a delivered; receipts (paid by payment) are M5b (DEC-026).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -802,9 +810,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -827,7 +835,11 @@
           <t>Refund automation</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>A sales credit note references one approved invoice of the same customer and currency (database rule), uses only the invoice's VAT codes at the invoice's rate versions (DEC-029), cannot exceed the invoice outstanding (service and database), is allocated to its invoice in the same transaction and is traceable from both documents. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1543,7 +1555,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts</t>
+          <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts M5a: Sales documents post only through the PostingService (SALES_INVOICE, SALES_CREDIT_NOTE, SALES_ALLOCATION_FX) and link to their journals both ways; architecture test: one writer of the sales tables, which never writes journals.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2494,9 +2506,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2519,7 +2531,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>An approved invoice posts exactly Dr trade receivables (gross) / Cr revenue (net per line) / Cr output VAT (per VAT-coded line), with standard, zero-rated and exempt lines and VAT-inclusive entry, hand-calculated. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
@@ -2690,9 +2706,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2715,7 +2731,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Sales: a credit note mirrors the credited lines and VAT, linked both ways (credit note -&gt; invoice; invoice lists its credit notes) and allocated. Purchases (debit notes) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
           <t>Sales credit notes M2; purchase (debit) notes M3. The reversal primitive and source linkage ship in M1</t>
@@ -3468,7 +3488,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Report -&gt; account -&gt; journal -&gt; source reference works (trial balance rows carry drill-down parameters; ledger lines carry journal and source). Source transaction and document links arrive with each source module. Tests: tests/api/ledger.test.ts</t>
+          <t>Report -&gt; account -&gt; journal -&gt; source reference works (trial balance rows carry drill-down parameters; ledger lines carry journal and source). Source transaction and document links arrive with each source module. Tests: tests/api/ledger.test.ts M5a: Journal -&gt; sales document drill path exists (source_id) and document -&gt; journal (journal_id); report drill-down UI is M8/M9.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3551,9 +3571,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3576,7 +3596,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Sales invoices: before approval, another approved invoice of the same customer with the same date, currency and total, or the same customer reference, refuses approval unless a reason is given (stored on the document and audited). Supplier bills (supplier's own number) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3706,9 +3730,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3731,7 +3755,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Closing a period is refused while draft sales documents are dated in it unless acknowledged (acknowledgeDraftDocuments, recorded on the audit event); drafts are listed by status. An age threshold and alerting (dashboard) are M8. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
@@ -3782,7 +3810,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). M2 adds ledger.request_created/approved/rejected/cancelled and ledger.policy_changed (before/after, reason). Source modules add their own events in M5+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
+          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). M2 adds ledger.request_created/approved/rejected/cancelled and ledger.policy_changed (before/after, reason). Source modules add their own events in M5+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts M5a: Sales documents audit created, updated, discarded, approved (with override reasons) and allocation events.</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
@@ -4169,7 +4197,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Journal -&gt; source via source_type/source_id/source_reference (done); source transaction -&gt; journal is delivered per source module (M2+).</t>
+          <t>Journal -&gt; source via source_type/source_id/source_reference (done); source transaction -&gt; journal is delivered per source module (M2+). M5a: Sales invoices, credit notes and allocations link to their journals and back (journal source_id; document journal_id; allocation fx_journal_id), proven by database rules.</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4279,7 +4307,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M5a: Close control for draft sales documents dated in the period (acknowledgement recorded); unreconciled bank items follow in M7.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4499,7 +4527,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2.</t>
+          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5200,7 +5228,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts</t>
+          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts M5a: Exercised end to end for credit-note allocations (M5a): carried amounts released by `releaseShare` (full remainder or prorated), difference posted as SALES_ALLOCATION_FX to the realised-FX account with receivables lines marked adjusts_currency; hand-calculated gain 20.00 and full-settlement 16.67 cases. Receipts and payments (M5b/M6) still to come.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5583,7 +5611,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Output VAT (sales codes) and input VAT (purchase codes) on journal lines, with visible VAT lines on the configured accounts. Invoices and bills are documents (M5/M6), so 'on invoices/bills' is not yet possible. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts</t>
+          <t>Output VAT (sales codes) and input VAT (purchase codes) on journal lines, with visible VAT lines on the configured accounts. Invoices and bills are documents (M5/M6), so 'on invoices/bills' is not yet possible. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts M5a: Sales invoices carry output VAT per line with the verified version at the document's tax point (M5a); purchase bills are M6.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
@@ -5636,7 +5664,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>A credit note entered as a debit on a sales code reduces output VAT (tested); linkage to the original supply needs documents (M5/M6).</t>
+          <t>A credit note entered as a debit on a sales code reduces output VAT (tested); linkage to the original supply needs documents (M5/M6). M5a: Sales credit notes adjust VAT at the rate version the invoice used, reported at the credit note's tax point (vat_rate_point proven by the database; workpaper test); purchase debit notes are M6. Rule UNVERIFIED (DEC-029).</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
@@ -5742,7 +5770,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Explicit tax point per journal (defaults to the journal date) selects the rate version and the return period (stagger function tested). Determining it from supply/invoice/payment dates is a document matter (M5/M6). Tests: tests/platform/vat.test.ts, tests/unit/vat-math.test.ts</t>
+          <t>Explicit tax point per journal (defaults to the journal date) selects the rate version and the return period (stagger function tested). Determining it from supply/invoice/payment dates is a document matter (M5/M6). Tests: tests/platform/vat.test.ts, tests/unit/vat-math.test.ts M5a: Sales documents carry issue date, supply date and tax point (explicit or the issue date); the view flags taxPointReview when they differ; statutory derivation not automated (DEC-028).</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
@@ -6272,7 +6300,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts</t>
+          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6.</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6351,9 +6379,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -6378,7 +6406,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>The snapshot function (name, kind, VAT number, account code, primary address, capture time) is delivered and tested; storing it on documents and proving history survives an edit after issue needs documents (M5/M6). Tests: tests/api/contact-roles.test.ts</t>
+          <t>The snapshot (name, kind, VAT number, account code, primary address, capture time) is stored on each sales document at approval and is proven unchanged after a later edit of the contact. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
@@ -6735,7 +6763,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -6751,7 +6779,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PLANNED - specification after M3/M4 design</t>
+          <t>M5a VERIFIED (e698562; v1-m5a-acceptance.md): invoices, credit notes, allocation with realised FX, reconciliation; M5b receipts specified; M5c (VAT on foreign-currency documents) to be specified (DEC-031)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6778,7 +6806,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -7033,7 +7061,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -7043,7 +7071,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -7053,7 +7081,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -7094,7 +7122,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6fb1938</t>
+          <t>e698562</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7134,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38311897860</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38318917124</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7195,6 +7223,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v2.6 (2026-10-12, DEC-026..031): M5a sales documents implemented. V1-MOD-06, V1-EX-01, V1-CON-04 -&gt; Implemented; V1-MOD-04, V1-EX-05, V1-CTL-02, V1-CTL-05 -&gt; Partially implemented (receipts M5b; purchases M6; alert thresholds M8); evidence extended on V1-CON-02, V1-ARC-01, MAN-ACC-06, MAN-ACC-08, XP-07, V1-VAT-04/05/07, V1-FX-07, V1-CTL-06, V1-RPT-02. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -704,9 +704,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Invoices: DRAFT (no number, no ledger effect; revisioned lines) -&gt; APPROVED (numbered without gaps from a locked sequence the database checks; customer snapshot; amounts recomputed with verified VAT rates; posted as SALES_INVOICE Dr receivables / Cr revenue / Cr output VAT; journal and document linked both ways; immutable) or DISCARDED; attachments through the evidence graph; drafts from ACCEPTED AI proposals, approval by people only; positive, negative, VAT (standard, zero, exempt; exclusive, inclusive), period-lock and correction-by-credit-note tests. 'Paid' is reached by credit notes now; by receipts in M5b. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+          <t>Invoices: DRAFT (no number, no ledger effect; revisioned lines) -&gt; APPROVED (numbered without gaps from a locked sequence the database checks; customer snapshot; amounts recomputed with verified VAT rates; posted as SALES_INVOICE Dr receivables / Cr revenue / Cr output VAT; journal and document linked both ways; immutable) or DISCARDED; attachments through the evidence graph; drafts from ACCEPTED AI proposals, approval by people only; positive, negative, VAT (standard, zero, exempt; exclusive, inclusive), period-lock and correction-by-credit-note tests. 'Paid' is reached by receipts and credit notes (M5b), with statements and aged receivables. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts Tests: tests/platform/sales-receipts.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>M5a delivered; receipts (paid by payment) are M5b (DEC-026).</t>
+          <t>M5a and M5b delivered (DEC-026, DEC-032).</t>
         </is>
       </c>
     </row>
@@ -912,9 +912,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -937,7 +937,11 @@
           <t>Direct debit integration</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Receipts post SALES_RECEIPT Dr bank or cash / Cr trade receivables when recorded; allocation to one or more invoices at entry or later; part payments; overpayments kept as unallocated credit (reducing open balance, credit-limit use and ageing); realised FX on every allocation when rates differ (gain 30.00 then loss 20.00, hand-calculated); duplicate check with reason; reversal of unallocated receipts at their own rate; database guards on immutability, allocation and reversal. Tests: tests/platform/sales-receipts.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2608,9 +2612,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2633,7 +2637,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>A receipt posts exactly Dr bank (or cash) / Cr trade receivables, in functional and foreign currency; its journal links to the receipt both ways. Tests: tests/platform/sales-receipts.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -4527,7 +4535,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7.</t>
+          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7. M5b adds `sales_receipt.recorded`.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5228,7 +5236,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts M5a: Exercised end to end for credit-note allocations (M5a): carried amounts released by `releaseShare` (full remainder or prorated), difference posted as SALES_ALLOCATION_FX to the realised-FX account with receivables lines marked adjusts_currency; hand-calculated gain 20.00 and full-settlement 16.67 cases. Receipts and payments (M5b/M6) still to come.</t>
+          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts M5a: Exercised end to end for credit-note allocations (M5a): carried amounts released by `releaseShare` (full remainder or prorated), difference posted as SALES_ALLOCATION_FX to the realised-FX account with receivables lines marked adjusts_currency; hand-calculated gain 20.00 and full-settlement 16.67 cases. Receipts and payments (M5b/M6) still to come. M5b: receipts settle foreign invoices with realised FX on every allocation, exercised end to end (two receipts at 0.90 and 0.80 against an invoice at 0.85: +30.00 / -20.00, net 10.00 = cash 860.00 less carried 850.00; no residue). Supplier payments are M6.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -6300,7 +6308,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6.</t>
+          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6. M5b: unallocated receipts also count as open (ending refused).</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6779,7 +6787,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>M5a VERIFIED (e698562; v1-m5a-acceptance.md): invoices, credit notes, allocation with realised FX, reconciliation; M5b receipts specified; M5c (VAT on foreign-currency documents) to be specified (DEC-031)</t>
+          <t>M5a VERIFIED (e698562); M5b implemented (receipts, allocation, realised FX, statement, ageing; acceptance package once verified); M5c (VAT on foreign-currency documents) to be specified (DEC-031)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6806,7 +6814,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7061,7 +7069,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -7071,7 +7079,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -7081,7 +7089,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -7122,7 +7130,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>e698562</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7142,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38318917124</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7154,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7230,6 +7238,13 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v2.7 (2026-10-13, DEC-032): M5b receipts implemented. V1-MOD-08, V1-EX-03 -&gt; Implemented; V1-MOD-04 -&gt; Implemented (paid by receipts); evidence extended on V1-FX-07 (end to end on receipts; payments M6), V1-CON-02, XP-07. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>M5a VERIFIED (e698562); M5b implemented (receipts, allocation, realised FX, statement, ageing; acceptance package once verified); M5c (VAT on foreign-currency documents) to be specified (DEC-031)</t>
+          <t>M5a VERIFIED (e698562; v1-m5a-acceptance.md); M5b VERIFIED (376aec6; v1-m5b-acceptance.md); M5c (VAT on foreign-currency documents) to be specified (DEC-031)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>376aec6</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38342847878</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -761,9 +761,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -786,8 +786,16 @@
           <t>Purchase orders, expense claims</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Bills: drafts with revisioned lines (default account from the supplier profile); approval takes an internal gapless number, stores the supplier snapshot, recomputes VAT with verified rates (input VAT and reverse charge) and posts PURCHASE_BILL Dr expense or asset / Dr input VAT / Cr trade payables; immutable after approval; duplicate check on the supplier's own number (case and spaces ignored) or same date and total, with a stored reason; separate approver; period-lock and close control; hand-calculated VAT boxes (1 25.00, 4 35.00, 7 320.33). Paying bills is M6b. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>M6a delivered; payments M6b (DEC-033).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -863,9 +871,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -888,7 +896,11 @@
           <t>Supplier refund workflow</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>A debit note credits one approved bill of the same supplier and currency (database rule), uses only the bill's VAT codes at its rate versions, mirrors the reverse-charge pair, cannot exceed the bill outstanding, is allocated on approval with realised FX (credit-normal), and is traceable from both documents. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2563,9 +2575,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2588,7 +2600,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>An approved bill posts exactly Dr expense (net per line) / Dr input VAT / Cr trade payables (gross), with zero-rated, exempt and reverse-charge lines (equal output and input VAT), hand-calculated. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2714,9 +2730,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2741,7 +2757,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Sales: a credit note mirrors the credited lines and VAT, linked both ways (credit note -&gt; invoice; invoice lists its credit notes) and allocated. Purchases (debit notes) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+          <t>Sales: a credit note mirrors the credited lines and VAT, linked both ways (credit note -&gt; invoice; invoice lists its credit notes) and allocated. Purchases (debit notes) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts M6a: purchase debit notes mirror the credited bill lines and VAT (reverse charge included), linked both ways and allocated. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3579,9 +3595,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3606,7 +3622,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Sales invoices: before approval, another approved invoice of the same customer with the same date, currency and total, or the same customer reference, refuses approval unless a reason is given (stored on the document and audited). Supplier bills (supplier's own number) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+          <t>Sales invoices: before approval, another approved invoice of the same customer with the same date, currency and total, or the same customer reference, refuses approval unless a reason is given (stored on the document and audited). Supplier bills (supplier's own number) are M6. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts M6a: bills are checked on the supplier's own invoice number (normalised) and on date, currency and total; override needs a reason. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -4315,7 +4331,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M5a: Close control for draft sales documents dated in the period (acknowledgement recorded); unreconciled bank items follow in M7.</t>
+          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M5a: Close control for draft sales documents dated in the period (acknowledgement recorded); unreconciled bank items follow in M7. M6a: the close control also counts draft purchase documents.</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5619,7 +5635,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Output VAT (sales codes) and input VAT (purchase codes) on journal lines, with visible VAT lines on the configured accounts. Invoices and bills are documents (M5/M6), so 'on invoices/bills' is not yet possible. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts M5a: Sales invoices carry output VAT per line with the verified version at the document's tax point (M5a); purchase bills are M6.</t>
+          <t>Output VAT (sales codes) and input VAT (purchase codes) on journal lines, with visible VAT lines on the configured accounts. Invoices and bills are documents (M5/M6), so 'on invoices/bills' is not yet possible. Tests: tests/platform/vat.test.ts, tests/api/vat.test.ts M5a: Sales invoices carry output VAT per line with the verified version at the document's tax point (M5a); purchase bills are M6. M6a: purchase bills carry input VAT and reverse charge per line with verified versions; workpaper boxes hand-calculated.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
@@ -5672,7 +5688,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>A credit note entered as a debit on a sales code reduces output VAT (tested); linkage to the original supply needs documents (M5/M6). M5a: Sales credit notes adjust VAT at the rate version the invoice used, reported at the credit note's tax point (vat_rate_point proven by the database; workpaper test); purchase debit notes are M6. Rule UNVERIFIED (DEC-029).</t>
+          <t>A credit note entered as a debit on a sales code reduces output VAT (tested); linkage to the original supply needs documents (M5/M6). M5a: Sales credit notes adjust VAT at the rate version the invoice used, reported at the credit note's tax point (vat_rate_point proven by the database; workpaper test); purchase debit notes are M6. Rule UNVERIFIED (DEC-029). M6a: debit notes adjust input VAT (and the reverse-charge pair, mirrored) at the bill's rate versions. Fix found: credits on BOTH-direction codes and reverse-charge credits posted to the wrong side before M6a; fixed and regression-tested.</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
@@ -5831,7 +5847,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Workpaper reconciliation: movement on the VAT accounts by journal date versus VAT lines by tax point, difference listed with the entries that explain it (non-VAT postings, tax points outside the journal's period). Tests: tests/platform/vat.test.ts (hand-calculated -9.50 example), tests/api/vat.test.ts</t>
+          <t>Workpaper reconciliation: movement on the VAT accounts by journal date versus VAT lines by tax point, difference listed with the entries that explain it (non-VAT postings, tax points outside the journal's period). Tests: tests/platform/vat.test.ts (hand-calculated -9.50 example), tests/api/vat.test.ts M6a: reverse charge on bills and debit notes (the pair follows the side of the net line).</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
@@ -6308,7 +6324,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6. M5b: unallocated receipts also count as open (ending refused).</t>
+          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6. M5b: unallocated receipts also count as open (ending refused). M6a: ending a supplier role is refused while it has drafts or bills with an amount outstanding.</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6814,7 +6830,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6830,7 +6846,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>M6a implemented (bills and debit notes; acceptance package once verified); M6b supplier payments and M6c cash transactions specified (DEC-033..036)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6857,7 +6873,7 @@
         <v>6</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7069,7 +7085,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -7079,7 +7095,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -7089,7 +7105,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -7130,7 +7146,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>376aec6</t>
+          <t>16c7f12</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7158,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38342847878</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7245,6 +7261,13 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v2.8 (2026-10-13, DEC-033/034): M6a purchase documents implemented. V1-MOD-07, V1-EX-02, V1-EX-05, V1-CTL-02 -&gt; Implemented; V1-MOD-05 -&gt; Partially implemented (payments M6b); evidence extended on V1-VAT-04/05/08, V1-CON-02, MAN-ACC-08, including two VAT direction fixes for credits. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6846,7 +6846,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M6a implemented (bills and debit notes; acceptance package once verified); M6b supplier payments and M6c cash transactions specified (DEC-033..036)</t>
+          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md): bills and debit notes; M6b supplier payments and M6c cash transactions specified (DEC-033..036)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38344953160</t>
         </is>
       </c>
     </row>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -761,9 +761,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Bills: drafts with revisioned lines (default account from the supplier profile); approval takes an internal gapless number, stores the supplier snapshot, recomputes VAT with verified rates (input VAT and reverse charge) and posts PURCHASE_BILL Dr expense or asset / Dr input VAT / Cr trade payables; immutable after approval; duplicate check on the supplier's own number (case and spaces ignored) or same date and total, with a stored reason; separate approver; period-lock and close control; hand-calculated VAT boxes (1 25.00, 4 35.00, 7 320.33). Paying bills is M6b. Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
+          <t>Bills: drafts with revisioned lines (default account from the supplier profile); approval takes an internal gapless number, stores the supplier snapshot, recomputes VAT with verified rates (input VAT and reverse charge) and posts PURCHASE_BILL Dr expense or asset / Dr input VAT / Cr trade payables; immutable after approval; duplicate check on the supplier's own number (case and spaces ignored) or same date and total, with a stored reason; separate approver; period-lock and close control; hand-calculated VAT boxes (1 25.00, 4 35.00, 7 320.33). Bills are paid by supplier payments (M6b). Tests: tests/platform/purchases.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (purchases section)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>M6a delivered; payments M6b (DEC-033).</t>
+          <t>M6a and M6b delivered (DEC-033..035).</t>
         </is>
       </c>
     </row>
@@ -977,9 +977,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1002,7 +1002,11 @@
           <t>Payment runs and bank file export</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Supplier payments post PURCHASE_PAYMENT Dr trade payables / Cr bank or cash when recorded; allocation to one or more bills at entry or later; part payments; prepayments kept as unallocated debit; realised FX on every allocation (loss 30.00 then gain 20.00, hand-calculated, net 10.00); duplicate check with reason; a payment while the supplier's stored bank details are UNVERIFIED is flagged (audited, filterable), never blocked (DEC-035); reversal of unallocated payments at their own rate; supplier statement and aged payables. Tests: tests/platform/purchase-payments.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (payments section)</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2681,9 +2685,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2706,7 +2710,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>A payment posts exactly Dr trade payables / Cr bank (or cash), in functional and foreign currency; linked both ways. Tests: tests/platform/purchase-payments.test.ts, tests/db/purchases.test.ts, tests/api/sales.test.ts (payments section)</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -4551,7 +4559,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7. M5b adds `sales_receipt.recorded`.</t>
+          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7. M5b adds `sales_receipt.recorded`. M6 adds `bill.approved`, `debit_note.approved` and `purchase_payment.recorded`.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5225,9 +5233,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5252,7 +5260,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts M5a: Exercised end to end for credit-note allocations (M5a): carried amounts released by `releaseShare` (full remainder or prorated), difference posted as SALES_ALLOCATION_FX to the realised-FX account with receivables lines marked adjusts_currency; hand-calculated gain 20.00 and full-settlement 16.67 cases. Receipts and payments (M5b/M6) still to come. M5b: receipts settle foreign invoices with realised FX on every allocation, exercised end to end (two receipts at 0.90 and 0.80 against an invoice at 0.85: +30.00 / -20.00, net 10.00 = cash 860.00 less carried 850.00; no residue). Supplier payments are M6.</t>
+          <t>Realised FX engine `settle` delivered and unit-tested (full settlement clears the carried value exactly; partial settlements prorate with no residue; gains and losses; refusals). No posting path or endpoint until receipts and payments exist (M5/M6), so not yet exercised end to end. Tests: tests/unit/fx-math.test.ts M5a: Exercised end to end for credit-note allocations (M5a): carried amounts released by `releaseShare` (full remainder or prorated), difference posted as SALES_ALLOCATION_FX to the realised-FX account with receivables lines marked adjusts_currency; hand-calculated gain 20.00 and full-settlement 16.67 cases. Receipts and payments (M5b/M6) still to come. M5b: receipts settle foreign invoices with realised FX on every allocation, exercised end to end (two receipts at 0.90 and 0.80 against an invoice at 0.85: +30.00 / -20.00, net 10.00 = cash 860.00 less carried 850.00; no residue). Supplier payments are M6. M6b: supplier payments settle foreign bills with realised FX on every allocation (credit-normal: -30.00 / +20.00), so receipts and payments both exercise it end to end.</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -6297,9 +6305,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -6324,7 +6332,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6. M5b: unallocated receipts also count as open (ending refused). M6a: ending a supplier role is refused while it has drafts or bills with an amount outstanding.</t>
+          <t>One contact holds both roles (tested); roles are created, changed, ended (with reason, never deleted) and reactivated with audit before/after. The rule 'ending is refused while open documents exist' cannot apply until documents exist (M5/M6) and is not yet implemented. Tests: tests/api/contact-roles.test.ts, tests/db/contact-roles.test.ts M5a: Ending a customer role is now refused while it has drafts or approved sales documents with an amount outstanding (tests/api/sales.test.ts); supplier documents follow in M6. M5b: unallocated receipts also count as open (ending refused). M6a: ending a supplier role is refused while it has drafts or bills with an amount outstanding. M6b: unallocated supplier payments also count as open; ending a role is now refused for open items of either role.</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6744,7 +6752,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6787,7 +6795,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -6846,7 +6854,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md): bills and debit notes; M6b supplier payments and M6c cash transactions specified (DEC-033..036)</t>
+          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md); M6b VERIFIED (a753db0; v1-m6b-acceptance.md); M6c cash transactions specified (DEC-036)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6873,7 +6881,7 @@
         <v>6</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -7085,7 +7093,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -7095,7 +7103,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -7105,7 +7113,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -7146,7 +7154,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16c7f12</t>
+          <t>a753db0</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7166,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38344953160</t>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38361606618</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7268,6 +7276,13 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v2.9 (2026-10-13, DEC-035): M6b supplier payments implemented. V1-MOD-09, V1-EX-04, V1-MOD-05, V1-FX-07, V1-CON-02 -&gt; Implemented; evidence extended on XP-07. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -1079,9 +1079,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1104,8 +1104,16 @@
           <t>Petty-cash float management</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Cash transactions (money in and out without a source document) post CASH_RECEIPT (Dr bank or cash / Cr income / Cr output VAT) or CASH_PAYMENT (Dr expense or asset / Dr input VAT / Cr bank or cash) when recorded, with VAT per line (standard, zero, exempt, reverse charge; exclusive or inclusive), hand-calculated (money in 255.00 with VAT 25.00; money out 105.00 inclusive with VAT 10.00; reverse charge 400.00 with the 50.00 pair; workpaper boxes 1 75.00, 4 60.00, 6 230.00, 7 495.00); duplicate check with reason; immutable; reversed once by a mirror journal that the database proves line by line; till receipts attachable as evidence. Negative cash at posting: cash in hand below zero on the date or any later date is refused without a reason (stored on the journal), for every posting by a person, and re-checked by the database at commit; an overdrawn bank account is a warning in the response and audit event (DEC-036, DEC-037). Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts, tests/api/sales.test.ts (cash section), tests/platform/purchase-payments.test.ts</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>M6c delivered (DEC-036, DEC-037). Company currency only (foreign-currency bank accounts M7; VAT on foreign currency M5c). Dashboard alerts are V1-CTL-04 (M8).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3713,9 +3721,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3738,8 +3746,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>At posting (M6c, DEC-036/037): every posting by a person that takes cash in hand below zero on its date or any later date is refused without a reason (PostingService, re-checked by the database at commit); an overdrawn bank account is returned as balanceWarnings and recorded on the audit event. Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>The dashboard and alert list for negative balances remain M8.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6854,7 +6870,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md); M6b VERIFIED (a753db0; v1-m6b-acceptance.md); M6c cash transactions specified (DEC-036)</t>
+          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md); M6b VERIFIED (a753db0; v1-m6b-acceptance.md); M6c cash transactions built (DEC-036/037), acceptance package after CI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6881,7 +6897,7 @@
         <v>6</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -7093,7 +7109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -7103,7 +7119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -7113,7 +7129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -7143,7 +7159,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7152,11 +7168,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>a753db0</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7164,11 +7176,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38361606618</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7178,7 +7186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7283,6 +7291,13 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v3.0 (2026-10-15, DEC-036/037): M6c cash transactions and the negative-cash control implemented. V1-MOD-11 -&gt; Implemented; V1-CTL-04 -&gt; Partially implemented (at posting; dashboard M8). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -6870,7 +6870,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md); M6b VERIFIED (a753db0; v1-m6b-acceptance.md); M6c cash transactions built (DEC-036/037), acceptance package after CI</t>
+          <t>M6a VERIFIED (16c7f12; v1-m6a-acceptance.md); M6b VERIFIED (a753db0; v1-m6b-acceptance.md); M6c VERIFIED (7f4adad; v1-m6c-acceptance.md)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7168,7 +7168,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7f4adad</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7176,7 +7180,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38798396155</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -1030,9 +1030,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1055,8 +1055,16 @@
           <t>Open Banking feeds (V11)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts (bank_account) sit on exactly one CURRENT_ASSET_BANK ledger account of the company (database-proven), with currency, bank name, sort code / account number / IBAN (mod-97 checked) / BIC encrypted with the platform field key and shown only masked (full details through an audited read by bank:manage), the bank's statement opening date and balance (fixed once lines exist), charges and interest accounts for M7b, close with reason. The ledger opening balance still goes through the M2 request. Tests: tests/platform/bank.test.ts, tests/db/bank.test.ts, tests/api/bank.test.ts</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>M7a delivered (DEC-039).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2803,9 +2811,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2828,7 +2836,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts are created over ledger accounts (one each, CURRENT_ASSET_BANK only, never deleted) and listed with ledger balance, statement balance and unmatched-line count. Tests: tests/platform/bank.test.ts, tests/db/bank.test.ts, tests/api/bank.test.ts</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2852,9 +2864,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2877,10 +2889,14 @@
           <t>OFX/MT940/Open Banking</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>CSV statements uploaded as scanned company documents are imported by the bank.statement.import job on the imports queue (progress, retries, failures and result on the job record; the worker never posts, ADR-61): column mapping by header or position, six date formats, signed or in/out amounts, optional running balance proved row by row in either file order, all or nothing with up to 100 row errors, the same file refused without a reason, overlapping lines skipped by fingerprint while genuine identical lines are kept, a wrong import voided while unmatched and re-imported. OFX/MT940/Open Banking deferred (DEC-038). Tests: tests/unit/bank-statements.test.ts, tests/platform/bank.test.ts, tests/db/bank.test.ts, tests/api/bank.test.ts (real worker)</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Asynchronous job with progress; file formats to be decided in the M4 design</t>
+          <t>M7a delivered (DEC-040).</t>
         </is>
       </c>
     </row>
@@ -2905,9 +2921,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2930,7 +2946,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Statement lines are stored only by their own import while it runs, linked to it, and never edited or deleted (database triggers and privileges); only `voided` (with the import) and the matched part (M7b, under its own flag) can move. Tests: tests/db/bank.test.ts</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3052,9 +3072,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3077,8 +3097,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>A transfer between two bank or cash accounts of the same currency posts one BANK_TRANSFER journal (Dr receiving / Cr paying) through the PostingService: the negative-cash rule applies to the paying side, an overdrawn bank warns; same foreign currency at one rate with no exchange difference; cross-currency refused (deferred, DEC-041); duplicate check with reason; mirror reversal proven by the database; never reversed in the ledger. Matching both statements to it is M7b. Tests: tests/platform/bank.test.ts, tests/db/bank.test.ts, tests/api/bank.test.ts</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Statement matching of transfers comes with M7b reconciliation.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -6913,7 +6941,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>M7a bank accounts, CSV statement import, statement lines, transfers built (DEC-038..041), acceptance package after CI; M7b reconciliation specified (DEC-042)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6928,7 +6956,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>To be written when the milestone is specified</t>
+          <t>Plan section 11: M7a imports (header, running balance, in/out columns, date formats, all-or-nothing row errors, duplicate file, overlap, identical genuine lines, void and re-import), transfers with the negative-cash rule, database guards, permissions and isolation; M7b as DEC-042.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6940,7 +6968,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7109,7 +7137,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -7129,7 +7157,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -7168,11 +7196,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7f4adad</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7180,11 +7204,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38798396155</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7209,7 +7229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7306,6 +7326,13 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v3.1 (2026-10-15, DEC-038..041): M7a bank accounts, CSV statement import (asynchronous, staged by the worker), statement lines and transfers implemented. V1-MOD-10, V1-BANK-01, V1-BANK-02, V1-BANK-03, V1-BANK-06 -&gt; Implemented. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -1458,9 +1458,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1483,8 +1483,16 @@
           <t>AI suggestions (V6)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Matches link statement lines to ledger entries on the bank account in the account currency, in full or in parts (one-to-many both ways), proved by the database (same account, same direction, never more than either side); states MATCHED / PARTIAL / UNMATCHED / VOID per line, suggestions on request, manual override with reason; the proof as at a date (statement and ledger balances each adjusted by their unmatched items; difference must be zero) and a sign-off that also requires the bank's printed closing balance to equal the imported statement, recorded once. Hand-calculated month: statement 514.75 = ledger 474.75 + unpresented cheque 40.00. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>M7b delivered (DEC-042).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2974,9 +2982,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2999,7 +3007,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliation workflow: suggestions -&gt; accept or match by hand (partial allowed) -&gt; post charges and interest from the statement -&gt; unmatched items -&gt; proof -&gt; sign-off; unmatch with reason at any time, flagged when a signed-off reconciliation covered it. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3023,9 +3035,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3048,8 +3060,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Unmatched items with ageing and counts per bank account are available through the API (unmatched list and the unmatched-line count on every bank account). Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>The dashboard screen that shows the count is M9.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3129,9 +3149,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3154,7 +3174,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>A statement line read as a bank charge is proposed for posting; a person posts it on the line's date as a cash transaction (Dr the account's charges account or one given / Cr bank, VAT code optional) through CashService and the PostingService, and it is matched in the same step; needs bank:reconcile and cash:record. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3178,9 +3202,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3203,7 +3227,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Interest received (Dr bank / Cr interest received) or paid (Dr interest paid / Cr bank) is proposed from the narrative and posted from the statement line the same way as charges. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3227,9 +3255,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3252,7 +3280,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>A match links one statement line to one ledger entry and is never edited or deleted (trigger and privileges); undoing it is an audited unmatch with a reason that keeps the row. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3276,9 +3308,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3301,7 +3333,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>A statement line (or a ledger entry) can be matched in parts; the unmatched remainder is shown on the line (PARTIAL) and in the unmatched list; the database keeps the matched part within the line and the ledger entry. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3325,9 +3361,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3350,7 +3386,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Unmatched statement lines and ledger entries as at a date, each with its age in days and buckets 0-7, 8-30, 31-60, 61+ (counts and totals); a later match does not rewrite an earlier date. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3374,9 +3414,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3399,7 +3439,11 @@
           <t>AI suggestions (V6)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Deterministic suggestions computed on request: same remaining amount, same direction, within 7 days; scored by date distance and the entry's reference appearing in the bank narrative; ties and a ledger entry suggested for two lines are flagged ambiguous; charge and interest proposals; a suggestion never matches or posts by itself. AI suggestions remain V6. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Rule-based suggestions; AI suggestions are V6 and may only propose</t>
@@ -3427,9 +3471,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3452,7 +3496,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>A match whose bank date and ledger date are more than 14 days apart needs an override reason (stored on the match and audited); every match records how it was made (MANUAL, SUGGESTION, POSTED_FROM_STATEMENT) and by whom; unmatching needs a reason. Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
@@ -6941,7 +6989,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>M7a bank accounts, CSV statement import, statement lines, transfers built (DEC-038..041), acceptance package after CI; M7b reconciliation specified (DEC-042)</t>
+          <t>M7a VERIFIED by CI (e100429; acceptance package v1-m7a-acceptance.md); M7b reconciliation built (DEC-042), acceptance package after CI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6968,7 +7016,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -7137,7 +7185,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -7147,7 +7195,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -7157,7 +7205,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -7229,7 +7277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7333,6 +7381,13 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v3.2 (2026-10-15, DEC-042): M7b reconciliation implemented. V1-MOD-18, V1-BANK-04, V1-BANK-07, V1-BANK-08, V1-REC-01..05 -&gt; Implemented; V1-BANK-05 -&gt; Partially implemented (API; the dashboard screen is M9). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -7244,7 +7244,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>b8c0e0a</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7252,7 +7256,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38811610801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -655,9 +655,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -680,8 +680,16 @@
           <t>Supplier portal</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Supplier role on the shared contact (M4a): payment terms, default currency and default expense account; bank details AES-GCM encrypted, never in lists, logs or audit (masked only), changes need a second person's verification; both roles allowed on one contact; an ended supplier role is refused on new bills and payments (contact_role_ended). Tests: tests/api/contact-roles.test.ts, tests/platform/purchases.test.ts, tests/platform/purchase-payments.test.ts, tests/unit/architecture.test.ts</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Correction recorded in v3.3: delivered by M4a (206b14d) and used by M6, but the row had not been updated. No code change.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1360,9 +1368,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1385,8 +1393,16 @@
           <t>FRS 102/105 layouts (V2)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Profit and loss for any range with a comparative range, from journal lines only through the versioned reporting mapping (turnover, cost of sales, gross profit, administrative expenses, other operating income, operating profit, interest, profit before tax, tax, profit for the period); each line lists its accounts with general-ledger drill parameters; reconciles to the net of income and expense accounts to the cent. Hand-calculated year: turnover 3,000.00, gross profit 2,700.00, operating profit 1,675.00, profit 1,685.00 (comparative 400.00). Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>M8 delivered (DEC-043). Statutory FRS 102/105 presentation, notes and rounding are V2.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1409,9 +1425,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1434,8 +1450,16 @@
           <t>FRS 102/105 layouts (V2)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Balance sheet as at any date with a comparative date, from journal lines only; capital and reserves include the P&amp;L cumulated to the date, split into brought forward and year to date (financial year = the accounting period containing the date); proves net assets = capital and reserves and that the trial balance balances. Hand-calculated: net assets 3,085.00 = 1,000.00 + 400.00 + 1,685.00. Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>M8 delivered (DEC-043).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1629,9 +1653,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1656,7 +1680,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Trial balance and general ledger aggregate journal_line only (architecture: no report reads source tables). P&amp;L and balance sheet are M5. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts</t>
+          <t>Statements are computed in ReportService from journal_line through the reporting mapping; an architecture test fails if reports.ts reads any source-document table or writes anything. Tests: tests/unit/architecture.test.ts, tests/platform/reports.test.ts</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3062,7 +3086,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Unmatched items with ageing and counts per bank account are available through the API (unmatched list and the unmatched-line count on every bank account). Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section)</t>
+          <t>Unmatched items with ageing and counts per bank account are available through the API (unmatched list and the unmatched-line count on every bank account). Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section) Alert list (M8): statement lines unmatched for longer than a threshold (default 30 days), by account. Tests: tests/platform/reports.test.ts</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3524,9 +3548,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3549,7 +3573,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>The P&amp;L equals income less expenses from the ledger for the range, and the balance sheet proves net assets = capital and reserves with a balanced trial balance, to the cent, for the current and the comparative period; the proofs are returned with each statement. Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Trial balance in M1</t>
@@ -3577,9 +3605,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3604,7 +3632,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Report -&gt; account -&gt; journal -&gt; source reference works (trial balance rows carry drill-down parameters; ledger lines carry journal and source). Source transaction and document links arrive with each source module. Tests: tests/api/ledger.test.ts M5a: Journal -&gt; sales document drill path exists (source_id) and document -&gt; journal (journal_id); report drill-down UI is M8/M9.</t>
+          <t>Statement line -&gt; accounts (with GL drill parameters) -&gt; general ledger -&gt; journal -&gt; source transaction (one resolver per journal source: documents, receipts, payments, allocations, cash transactions, transfers, requests, revaluations, reversals) -&gt; attached documents; readers without the module permission see that a source exists but not its content. A unit test fails if a journal source lacks a resolver; the platform test drills every source type in a full set of books. Tests: tests/unit/drilldown.test.ts, tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3767,12 +3795,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Trial balance warns about a non-zero suspense balance (account with control kind SUSPENSE). Dashboard alert is M5. Tests: tests/platform/posting-service.test.ts</t>
+          <t>The suspense balance is an alert (HIGH) as at any date, and locking a period whose end shows a suspense balance is refused unless acknowledged with a reason (recorded). Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Trial balance warning in M1; dashboard alert in M5</t>
+          <t>The dashboard screen is M9.</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3852,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>At posting (M6c, DEC-036/037): every posting by a person that takes cash in hand below zero on its date or any later date is refused without a reason (PostingService, re-checked by the database at commit); an overdrawn bank account is returned as balanceWarnings and recorded on the audit event. Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts</t>
+          <t>At posting (M6c, DEC-036/037): every posting by a person that takes cash in hand below zero on its date or any later date is refused without a reason (PostingService, re-checked by the database at commit); an overdrawn bank account is returned as balanceWarnings and recorded on the audit event. Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts Alert list (M8): negative cash in hand and overdrawn bank accounts as at a date. Tests: tests/platform/reports.test.ts</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>The dashboard and alert list for negative balances remain M8.</t>
+          <t>At posting (M6c) and in the alert list (M8: negative cash HIGH, overdrawn bank MEDIUM); the dashboard screen is M9.</t>
         </is>
       </c>
     </row>
@@ -3854,9 +3882,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3881,7 +3909,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Closing a period is refused while draft sales documents are dated in it unless acknowledged (acknowledgeDraftDocuments, recorded on the audit event); drafts are listed by status. An age threshold and alerting (dashboard) are M8. Tests: tests/platform/sales.test.ts, tests/db/sales.test.ts, tests/api/sales.test.ts, tests/unit/sales-math.test.ts</t>
+          <t>Sales and purchase drafts older than a threshold (default 14 days) are listed in the alert list, shown only to readers of the module; closing a period with drafts dated in it is refused unless acknowledged (recorded on the audit event). Tests: tests/platform/reports.test.ts, tests/platform/sales.test.ts, tests/platform/purchases.test.ts</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
@@ -4294,9 +4322,9 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4321,7 +4349,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Journal -&gt; source via source_type/source_id/source_reference (done); source transaction -&gt; journal is delivered per source module (M2+). M5a: Sales invoices, credit notes and allocations link to their journals and back (journal source_id; document journal_id; allocation fx_journal_id), proven by database rules.</t>
+          <t>Every journal source maps to its source transaction and back (source_id on the journal; journal_id on the record); the drill-down resolver list is tested to cover every source type. Tests: tests/unit/drilldown.test.ts, tests/platform/reports.test.ts</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4351,9 +4379,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4376,7 +4404,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Every statement figure is drillable to accounts, ledger lines, journals, source transactions and documents (V1-RPT-02). Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
+        </is>
+      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
           <t>Same as V1-RPT-02</t>
@@ -4404,9 +4436,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4431,7 +4463,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Explicit period states and the transition graph are delivered and enforced; the close controls so far are 'posting stops' and 'ledger balances'. Unposted documents and unreconciled bank items are added by M2-M4. Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M5a: Close control for draft sales documents dated in the period (acknowledgement recorded); unreconciled bank items follow in M7. M6a: the close control also counts draft purchase documents.</t>
+          <t>Period close checks: ledger balances; FX revaluation and due reversals; draft sales and purchase documents; bank statement lines dated in the period not fully reconciled (acknowledgeUnreconciledBank); period lock checks the suspense balance (acknowledgeSuspenseBalance). Each acknowledgement is recorded with its figures on the audit event. Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4575,9 +4607,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4600,7 +4632,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>One drill-down endpoint (GET journals/{id}/source) serves every report and journal, with one resolver per source type. Tests: tests/unit/drilldown.test.ts, tests/api/reports.test.ts</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
@@ -5439,9 +5475,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5466,12 +5502,12 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Reconciliation proven: after revaluation, original balance x closing rate equals the functional carrying amount per account (tests/platform/fx.test.ts); the functional-currency trial balance balances and the FX accounts' general ledger drills to the revaluation journal and its reversal (tests/api/fx.test.ts). A dedicated FX gain/loss report and multi-currency statements belong with reporting (M8).</t>
+          <t>FX report for a range: realised (allocation journals) and unrealised (revaluations and reversals) differences by currency with their journals, each drillable; open foreign-currency monetary balances against the closing rate with the difference a revaluation would post, zero once revalued; the functional trial balance balances and the P&amp;L reconciles with FX lines included. Hand-calculated: realised gain 30.00, unrealised loss 80.00 (-20.00 receivable, -60.00 bank) reversed the next day. Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Multi-currency reporting checks repeat in M8</t>
+          <t>M8 delivered (DEC-045).</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6794,7 @@
         <v>33</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -6844,7 +6880,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -6887,7 +6923,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -6930,7 +6966,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -7032,7 +7068,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>M8 built (DEC-043..045): statements, drill-down, alerts, close controls, FX report; acceptance package after CI</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7047,7 +7083,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>To be written when the milestone is specified</t>
+          <t>Plan section 12: a hand-calculated year through every sub-ledger with comparatives, reconciling to the trial balance to the cent; drill-down for every journal source; alerts raised and filtered; close and lock refused and acknowledged; the FX report against the revaluation.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7059,7 +7095,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -7185,7 +7221,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -7195,7 +7231,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -7205,7 +7241,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -7244,11 +7280,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>b8c0e0a</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7256,11 +7288,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/UK-Accounting-Platform/actions/runs/38811610801</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7285,7 +7313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7396,6 +7424,13 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v3.3 (2026-10-15, DEC-043..045): M8 reports implemented. V1-MOD-16, V1-MOD-17, V1-ARC-02, V1-RPT-01, V1-RPT-02, MAN-ACC-06, MAN-ACC-07, XP-01, V1-CTL-05, MAN-ACC-08, V1-FX-09 -&gt; Implemented; V1-CTL-03 -&gt; Partially implemented (dashboard screen M9); evidence extended on V1-CTL-04 and V1-BANK-05. Correction: V1-MOD-03 -&gt; Implemented (delivered by M4a, row not updated then). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -602,9 +602,9 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,10 +627,14 @@
           <t>Statements, dunning</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>M8h (DEC-046): with M4a's customer role (terms, credit limit, default currency, filter/search by role, company-scoped, both roles, ended roles refused on new documents), the customer now carries a default sales VAT code (database: same organisation, sales or both, not reverse charge; service: same check). Invoice lines without a code take it when written, `null` keeps none, credit notes and foreign-currency drafts are unaffected, and a later change never alters a document; changes are audited before/after. Tests: tests/api/sales.test.ts (customer default VAT code), tests/db/contact-roles.test.ts, tests/api/contact-roles.test.ts.</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>V0 contacts exist (master data); customer role/terms are V1</t>
+          <t>Statements and dunning deferred</t>
         </is>
       </c>
     </row>
@@ -1596,9 +1600,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1623,7 +1627,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts M5a: Sales documents post only through the PostingService (SALES_INVOICE, SALES_CREDIT_NOTE, SALES_ALLOCATION_FX) and link to their journals both ways; architecture test: one writer of the sales tables, which never writes journals.</t>
+          <t>PostingService -&gt; journal -&gt; journal_line -&gt; ledger exists with MANUAL, OPENING_BALANCE and REVERSAL sources. No source-document transaction services yet (M2+). Tests: tests/platform/posting-service.test.ts M5a: Sales documents post only through the PostingService (SALES_INVOICE, SALES_CREDIT_NOTE, SALES_ALLOCATION_FX) and link to their journals both ways; architecture test: one writer of the sales tables, which never writes journals. M5-M8: every source module posts only through the PostingService (architecture tests: one writer per sub-ledger table, no journal writes outside posting.ts; sales, purchases, cash, bank, reconciliation via CashService; the worker never posts). Each journal names its source (source_type, source_id) and each source row its journal(s); DrillDownService resolves every journal source to its transaction (tests/unit/drilldown.test.ts) and tests/platform/reports.test.ts drills from every kind of journal in the books to its document.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2411,9 +2415,9 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2438,12 +2442,12 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Currency validated: journals are in the company base currency and amounts respect its minor units (application + database). Foreign-currency documents, FX rates and revaluation are NOT supported (open decision 1). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+          <t>Currency validated: journals are in the company base currency and amounts respect its minor units (application + database). Foreign-currency documents, FX rates and revaluation are NOT supported (open decision 1). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M3 (accepted, DEC-019): transaction currency, rate (stored, manual or looked up) and original amounts are validated and kept per line; per-line half-up conversion with a visible rounding line; VAT on foreign-currency journals refused until M5c. Tests: tests/platform/fx.test.ts, tests/db/fx.test.ts, tests/unit/fx-math.test.ts.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Base currency of the company only; foreign-currency postings and FX revaluation are not in V1 scope until a decision is recorded</t>
+          <t>Multi-currency delivered by M3; VAT on foreign-currency documents is M5c (V1-VAT-15)</t>
         </is>
       </c>
     </row>
@@ -3935,9 +3939,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3962,7 +3966,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). M2 adds ledger.request_created/approved/rejected/cancelled and ledger.policy_changed (before/after, reason). Source modules add their own events in M5+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts M5a: Sales documents audit created, updated, discarded, approved (with override reasons) and allocation events.</t>
+          <t>journal.posted/reversed, account.created/updated/chart_initialised and period.closed/reopened/locked/unlocked are audited in the business transaction (before/after, reason, actor, source workflow where relevant). M2 adds ledger.request_created/approved/rejected/cancelled and ledger.policy_changed (before/after, reason). Source modules add their own events in M5+. Tests: tests/platform/posting-service.test.ts, tests/api/ledger.test.ts M5a: Sales documents audit created, updated, discarded, approved (with override reasons) and allocation events. M5-M8: every source module audits its actions with actor, before/after and reason: sales and purchase documents (created, updated, discarded, approved, allocations), receipts and payments (recorded, reversed), cash transactions (recorded, reversed), bank accounts, imports, transfers, matches and sign-offs, periods. M8h test: every journal of two companies' books has its journal.posted/reversed event by the person, and each sub-ledger action its own event (tests/platform/posting-rules.test.ts, audit trail of every source module).</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
@@ -3988,9 +3992,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Positive, negative, reversal and period-lock tests exist for every M1 posting rule; the VAT test arrives with the VAT validator (M2). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts</t>
+          <t>Positive, negative, reversal and period-lock tests exist for every M1 posting rule; the VAT test arrives with the VAT validator (M2). Tests: tests/platform/posting-service.test.ts, tests/db/ledger.test.ts M8h (DEC-047): coverage registry tests/rules/posting-rules.ts names, for all 21 journal sources, the positive, negative, reversal, VAT and period-lock test (or a design reason: only the reversal of a mirror or of a credit/debit note is n/a). tests/unit/posting-rule-coverage.test.ts fails when a source, category, file or test title is missing. Gaps filled in tests/platform/posting-rules.test.ts: closed and locked periods per source through its own service (14 sources had none), VAT refused on every source without `vatCodes` (new registry flag enforced by the PostingService), control kinds per sub-ledger source, allocation FX journals final in the ledger, cash-receipt reversal VAT mirror.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4660,9 +4664,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7. M5b adds `sales_receipt.recorded`. M6 adds `bill.approved`, `debit_note.approved` and `purchase_payment.recorded`.</t>
+          <t>transaction.posted and accounting_period.state_changed events are published through the outbox; BankImported and InvoiceCreated arrive with M4 and M2. M5a: InvoiceCreated (`invoice.created`) and `credit_note.created` are published through the outbox on approval (tests/platform/sales.test.ts); BankImported is M7. M5b adds `sales_receipt.recorded`. M6 adds `bill.approved`, `debit_note.approved` and `purchase_payment.recorded`. M7a: BankImported (`bank_statement.imported`) is published through the outbox when a statement import completes (tests/platform/bank.test.ts asserts the outbox row). With TransactionPosted (M1) and InvoiceCreated (M5a) all three named events are delivered.</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6794,7 +6798,7 @@
         <v>33</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6880,7 +6884,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -6923,7 +6927,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -7221,7 +7225,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -7231,7 +7235,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -7241,7 +7245,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -7313,7 +7317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7431,6 +7435,13 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v3.4 (2026-10-15, DEC-046/047, M8h): V1-MOD-02 -&gt; Implemented (customer default VAT code); V1-TEST-01 -&gt; Implemented (posting-rule coverage registry and its gap tests); V1-ARC-01, V1-POST-06, XP-07, V1-CTL-06 -&gt; Implemented on evidence re-checked against their acceptance criteria (no code change except the audit-trail test). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -3063,9 +3063,9 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3090,14 +3090,10 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Unmatched items with ageing and counts per bank account are available through the API (unmatched list and the unmatched-line count on every bank account). Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section) Alert list (M8): statement lines unmatched for longer than a threshold (default 30 days), by account. Tests: tests/platform/reports.test.ts</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>The dashboard screen that shows the count is M9.</t>
-        </is>
-      </c>
+          <t>Unmatched items with ageing and counts per bank account are available through the API (unmatched list and the unmatched-line count on every bank account). Tests: tests/platform/reconciliation.test.ts, tests/db/reconciliation.test.ts, tests/api/bank.test.ts (reconciliation section) Alert list (M8): statement lines unmatched for longer than a threshold (default 30 days), by account. Tests: tests/platform/reports.test.ts M9a: the dashboard shows the count of statement lines unmatched beyond the threshold (from GET alerts, visible to bank:read readers) next to the other key controls; tests/e2e/workspace.test.ts. The reconciliation screens are M9c.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3772,9 +3768,9 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3799,14 +3795,10 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>The suspense balance is an alert (HIGH) as at any date, and locking a period whose end shows a suspense balance is refused unless acknowledged with a reason (recorded). Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>The dashboard screen is M9.</t>
-        </is>
-      </c>
+          <t>The suspense balance is an alert (HIGH) as at any date, and locking a period whose end shows a suspense balance is refused unless acknowledged with a reason (recorded). Tests: tests/platform/reports.test.ts, tests/api/reports.test.ts M9a (DEC-048..050): the company dashboard shows it first, from GET alerts as the API computed it, with a drill link to the account's ledger; real-browser test tests/e2e/workspace.test.ts. Locking with a suspense balance stays refused unless acknowledged with a reason (M8); the periods screen shows the API's refusal and offers that acknowledgement.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3829,9 +3821,9 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3856,14 +3848,10 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>At posting (M6c, DEC-036/037): every posting by a person that takes cash in hand below zero on its date or any later date is refused without a reason (PostingService, re-checked by the database at commit); an overdrawn bank account is returned as balanceWarnings and recorded on the audit event. Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts Alert list (M8): negative cash in hand and overdrawn bank accounts as at a date. Tests: tests/platform/reports.test.ts</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>At posting (M6c) and in the alert list (M8: negative cash HIGH, overdrawn bank MEDIUM); the dashboard screen is M9.</t>
-        </is>
-      </c>
+          <t>At posting (M6c, DEC-036/037): every posting by a person that takes cash in hand below zero on its date or any later date is refused without a reason (PostingService, re-checked by the database at commit); an overdrawn bank account is returned as balanceWarnings and recorded on the audit event. Tests: tests/platform/cash.test.ts, tests/db/cash.test.ts Alert list (M8): negative cash in hand and overdrawn bank accounts as at a date. Tests: tests/platform/reports.test.ts M9a (DEC-048..050): the company dashboard shows it first, from GET alerts as the API computed it, with a drill link to the account's ledger; real-browser test tests/e2e/workspace.test.ts. (cash in hand below zero and overdrawn bank, shown together).</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4721,9 +4709,9 @@
           <t>M9</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4746,7 +4734,11 @@
           <t>Mobile portal</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>M9a: workspace screens usable in a real browser behind bookkeeping.core (dashboard, accounts, journals with drill-down, trial balance, general ledger, P&amp;L, balance sheet, periods with the close and lock controls); a my-access endpoint hides what the person may not do while the API still enforces. Tests: tests/e2e/workspace.test.ts, tests/api/my-access.test.ts. Sales, purchases (M9b), bank, cash and reconciliation (M9c) screens remain.</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>DEC-002: parallel behind feature flags</t>
@@ -6798,7 +6790,7 @@
         <v>33</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -7056,7 +7048,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -7099,7 +7091,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -7225,7 +7217,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -7235,7 +7227,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -7245,7 +7237,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7317,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7442,6 +7434,13 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v3.5 (2026-10-15, DEC-048..050, M9a): V1-CTL-03, V1-CTL-04, V1-BANK-05 -&gt; Implemented (the dashboard criterion met by the M9a workspace, real-browser tested); V1-DOD-01 Missing -&gt; Partially implemented (M9a screens; M9b and M9c remain). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>M8 built (DEC-043..045): statements, drill-down, alerts, close controls, FX report; acceptance package after CI</t>
+          <t>M8 verified (code baseline b1e69af; v1-m8-acceptance.md); M8h hygiene verified (e358a26; v1-m8h-acceptance.md)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PLANNED - runs in parallel from M2</t>
+          <t>M9a verified (34c2c1e; v1-m9a-acceptance.md): workspace screens behind bookkeeping.core; M9b sales and purchases, M9c bank, cash and reconciliation to follow</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7276,7 +7276,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>34c2c1e</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7284,7 +7288,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/38822337045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -4736,7 +4736,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>M9a: workspace screens usable in a real browser behind bookkeeping.core (dashboard, accounts, journals with drill-down, trial balance, general ledger, P&amp;L, balance sheet, periods with the close and lock controls); a my-access endpoint hides what the person may not do while the API still enforces. Tests: tests/e2e/workspace.test.ts, tests/api/my-access.test.ts. Sales, purchases (M9b), bank, cash and reconciliation (M9c) screens remain.</t>
+          <t>M9a: workspace screens usable in a real browser behind bookkeeping.core (dashboard, accounts, journals with drill-down, trial balance, general ledger, P&amp;L, balance sheet, periods with the close and lock controls); a my-access endpoint hides what the person may not do while the API still enforces. Tests: tests/e2e/workspace.test.ts, tests/api/my-access.test.ts. Sales, purchases (M9b), bank, cash and reconciliation (M9c) screens remain. M9b: sales and purchases screens (documents, new invoice and bill, approve, discard, full credit and debit notes, receipts and payments with allocation and reversal, ageing, statements) with the API's override prompts; tests/e2e/subledger.test.ts.</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -7276,11 +7276,7 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>34c2c1e</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7288,11 +7284,7 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/38822337045</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7302,7 +7294,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7449,6 +7441,13 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v3.6 (2026-10-16, M9b): evidence added to V1-DOD-01 (sales and purchases screens); no status changes. No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -4709,9 +4709,9 @@
           <t>M9</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>M9a: workspace screens usable in a real browser behind bookkeeping.core (dashboard, accounts, journals with drill-down, trial balance, general ledger, P&amp;L, balance sheet, periods with the close and lock controls); a my-access endpoint hides what the person may not do while the API still enforces. Tests: tests/e2e/workspace.test.ts, tests/api/my-access.test.ts. Sales, purchases (M9b), bank, cash and reconciliation (M9c) screens remain. M9b: sales and purchases screens (documents, new invoice and bill, approve, discard, full credit and debit notes, receipts and payments with allocation and reversal, ageing, statements) with the API's override prompts; tests/e2e/subledger.test.ts.</t>
+          <t>M9a: workspace screens usable in a real browser behind bookkeeping.core (dashboard, accounts, journals with drill-down, trial balance, general ledger, P&amp;L, balance sheet, periods with the close and lock controls); a my-access endpoint hides what the person may not do while the API still enforces. Tests: tests/e2e/workspace.test.ts, tests/api/my-access.test.ts. Sales, purchases (M9b), bank, cash and reconciliation (M9c) screens remain. M9b: sales and purchases screens (documents, new invoice and bill, approve, discard, full credit and debit notes, receipts and payments with allocation and reversal, ageing, statements) with the API's override prompts; tests/e2e/subledger.test.ts. M9c: bank accounts, CSV statement import through the screen, reconciliation with suggestions, matching, posting from the statement, proof and sign-off, cash transactions and transfers; tests/e2e/bank.test.ts. All three slices accepted (v1-m9a/m9b/m9c-acceptance.md).</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>DEC-002: parallel behind feature flags</t>
+          <t>Screens are functional, not designed; behind bookkeeping.core; not production-approved</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>M9a verified (34c2c1e; v1-m9a-acceptance.md): workspace screens behind bookkeeping.core; M9b sales and purchases, M9c bank, cash and reconciliation to follow</t>
+          <t>M9 verified: M9a (34c2c1e), M9b (5854a0d), M9c (c0cad12); acceptance packages v1-m9a/m9b/m9c-acceptance.md; screens behind bookkeeping.core</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -7276,7 +7276,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>c0cad12</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7284,7 +7288,11 @@
           <t>CI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://github.com/mianshoaiblhr/uk-accounting-platform/actions/runs/38973214119</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7309,7 +7317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7448,6 +7456,13 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v3.7 (2026-10-16, M9c): V1-DOD-01 Partially -&gt; Implemented (every V1 module has screens: M9a workspace, M9b sales and purchases, M9c bank, cash and reconciliation; real-browser tests 21/21; CI 38973214119). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/architecture/v1-compliance-matrix.xlsx
+++ b/docs/architecture/v1-compliance-matrix.xlsx
@@ -4517,7 +4517,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Reporting mappings versioned in M1; VAT rates effective-dated in M2</t>
+          <t>Decided in DEC-051: reporting maps move into the database in V2-M1; tracked from now in the V2 matrix (row MAN-ACC-09). VAT rates are already effective-dated (M4b).</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -7463,6 +7463,13 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v3.8 (2026-10-17, DEC-051): MAN-ACC-09 note: decided (reporting maps into the database in V2-M1) and carried to the V2 matrix; status unchanged (Partially). No rows added or removed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
